--- a/GWD Data/GWD MR Abstract.xlsx
+++ b/GWD Data/GWD MR Abstract.xlsx
@@ -32,7 +32,7 @@
     <t>Index</t>
   </si>
   <si>
-    <t>PTA</t>
+    <t>TVM</t>
   </si>
   <si>
     <t>Sl No</t>
@@ -1543,6 +1543,7 @@
       <sheetName val="GWD DR Abstract"/>
       <sheetName val="GWD MR Abstract"/>
       <sheetName val="3 Core Cable PRICE"/>
+      <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
@@ -1618,6 +1619,7 @@
       <sheetData sheetId="35"/>
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1939,7 +1941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97DA0DCE-6014-47FC-960A-4B9D6B4BB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B3F80A-05D2-4DB7-9DA1-227D42C7B9A6}">
   <dimension ref="A1:L197"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -1979,7 +1981,7 @@
       <c r="K2" s="5"/>
       <c r="L2" s="11">
         <f t="array" ref="L2">((IFERROR(INDEX(CostIndex,MATCH(J2,District,0),),)))</f>
-        <v>1.4444999999999999</v>
+        <v>1.4765999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="12.75">
@@ -2054,11 +2056,11 @@
       </c>
       <c r="K4" s="16">
         <f>J4*($L$2-1)</f>
-        <v>13.779500000000001</v>
+        <v>14.7746</v>
       </c>
       <c r="L4" s="16">
         <f>SUM(I4:K4)</f>
-        <v>124.7795</v>
+        <v>125.77460000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="12.75">
@@ -2095,11 +2097,11 @@
       </c>
       <c r="K5" s="16">
         <f>J5*($L$2-1)</f>
-        <v>15.5575</v>
+        <v>16.681000000000001</v>
       </c>
       <c r="L5" s="16">
         <f>SUM(I5:K5)</f>
-        <v>200.5575</v>
+        <v>201.68100000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="12.75">
@@ -2136,11 +2138,11 @@
       </c>
       <c r="K6" s="16">
         <f>J6*($L$2-1)</f>
-        <v>16.4465</v>
+        <v>17.6342</v>
       </c>
       <c r="L6" s="16">
         <f>SUM(I6:K6)</f>
-        <v>91.9465</v>
+        <v>93.134200000000007</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="12.75">
@@ -2177,11 +2179,11 @@
       </c>
       <c r="K7" s="16">
         <f>J7*($L$2-1)</f>
-        <v>17.557749999999999</v>
+        <v>18.825700000000001</v>
       </c>
       <c r="L7" s="16">
         <f>SUM(I7:K7)</f>
-        <v>98.257750000000001</v>
+        <v>99.525700000000001</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="12.75">
@@ -2218,11 +2220,11 @@
       </c>
       <c r="K8" s="16">
         <f>J8*($L$2-1)</f>
-        <v>19.558</v>
+        <v>20.970400000000001</v>
       </c>
       <c r="L8" s="16">
         <f>SUM(I8:K8)</f>
-        <v>111.358</v>
+        <v>112.7704</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="12.75">
@@ -2259,11 +2261,11 @@
       </c>
       <c r="K9" s="16">
         <f>J9*($L$2-1)</f>
-        <v>21.558250000000001</v>
+        <v>23.115100000000002</v>
       </c>
       <c r="L9" s="16">
         <f>SUM(I9:K9)</f>
-        <v>122.55825</v>
+        <v>124.1151</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="12.75">
@@ -2546,11 +2548,11 @@
       </c>
       <c r="K16" s="16">
         <f>J16*($L$2-1)</f>
-        <v>14.44625</v>
+        <v>15.4895</v>
       </c>
       <c r="L16" s="16">
         <f>SUM(I16:K16)</f>
-        <v>131.94625</v>
+        <v>132.98949999999999</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.75">
@@ -2587,11 +2589,11 @@
       </c>
       <c r="K17" s="16">
         <f>J17*($L$2-1)</f>
-        <v>16.001999999999999</v>
+        <v>17.157599999999999</v>
       </c>
       <c r="L17" s="16">
         <f>SUM(I17:K17)</f>
-        <v>212.00200000000001</v>
+        <v>213.1576</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.75">
@@ -2628,11 +2630,11 @@
       </c>
       <c r="K18" s="16">
         <f>J18*($L$2-1)</f>
-        <v>16.66875</v>
+        <v>17.8725</v>
       </c>
       <c r="L18" s="16">
         <f>SUM(I18:K18)</f>
-        <v>244.16875</v>
+        <v>245.3725</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="12.75">
@@ -3325,11 +3327,11 @@
       </c>
       <c r="K35" s="16">
         <f>J35*($L$2-1)</f>
-        <v>14.001749999999999</v>
+        <v>15.0129</v>
       </c>
       <c r="L35" s="16">
         <f>SUM(I35:K35)</f>
-        <v>90.501750000000001</v>
+        <v>91.512900000000002</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="12.75">
@@ -3366,11 +3368,11 @@
       </c>
       <c r="K36" s="16">
         <f>J36*($L$2-1)</f>
-        <v>16.890999999999998</v>
+        <v>18.110800000000001</v>
       </c>
       <c r="L36" s="16">
         <f>SUM(I36:K36)</f>
-        <v>134.89099999999999</v>
+        <v>136.11080000000001</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="12.75">
@@ -3407,11 +3409,11 @@
       </c>
       <c r="K37" s="16">
         <f>J37*($L$2-1)</f>
-        <v>18.669</v>
+        <v>20.017199999999999</v>
       </c>
       <c r="L37" s="16">
         <f>SUM(I37:K37)</f>
-        <v>155.66900000000001</v>
+        <v>157.0172</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="12.75">
@@ -4022,11 +4024,11 @@
       </c>
       <c r="K52" s="16">
         <f>J52*($L$2-1)</f>
-        <v>12.65047</v>
+        <v>13.564036</v>
       </c>
       <c r="L52" s="16">
         <f>SUM(I52:K52)</f>
-        <v>59.610469999999999</v>
+        <v>60.524036000000002</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="12.75">
@@ -4063,11 +4065,11 @@
       </c>
       <c r="K53" s="16">
         <f>J53*($L$2-1)</f>
-        <v>12.65047</v>
+        <v>13.564036</v>
       </c>
       <c r="L53" s="16">
         <f>SUM(I53:K53)</f>
-        <v>63.610469999999999</v>
+        <v>64.524035999999995</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="12.75">
@@ -4104,11 +4106,11 @@
       </c>
       <c r="K54" s="16">
         <f>J54*($L$2-1)</f>
-        <v>12.65047</v>
+        <v>13.564036</v>
       </c>
       <c r="L54" s="16">
         <f>SUM(I54:K54)</f>
-        <v>66.610470000000007</v>
+        <v>67.524035999999995</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="12.75">
@@ -4145,11 +4147,11 @@
       </c>
       <c r="K55" s="16">
         <f>J55*($L$2-1)</f>
-        <v>13.232765000000001</v>
+        <v>14.188382000000001</v>
       </c>
       <c r="L55" s="16">
         <f>SUM(I55:K55)</f>
-        <v>71.462765000000005</v>
+        <v>72.418381999999994</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="12.75">
@@ -4343,7 +4345,7 @@
         <v>137</v>
       </c>
       <c r="I60" s="14">
-        <v>96</v>
+        <v>51.11</v>
       </c>
       <c r="J60" s="14">
         <v>0</v>
@@ -4354,7 +4356,7 @@
       </c>
       <c r="L60" s="16">
         <f>SUM(I60:K60)</f>
-        <v>96</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="12.75">
@@ -4384,7 +4386,7 @@
         <v>137</v>
       </c>
       <c r="I61" s="14">
-        <v>114</v>
+        <v>69.69</v>
       </c>
       <c r="J61" s="14">
         <v>0</v>
@@ -4395,7 +4397,7 @@
       </c>
       <c r="L61" s="16">
         <f>SUM(I61:K61)</f>
-        <v>114</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="12.75">
@@ -4425,7 +4427,7 @@
         <v>137</v>
       </c>
       <c r="I62" s="14">
-        <v>168</v>
+        <v>92.92</v>
       </c>
       <c r="J62" s="14">
         <v>0</v>
@@ -4436,7 +4438,7 @@
       </c>
       <c r="L62" s="16">
         <f>SUM(I62:K62)</f>
-        <v>168</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="12.75">
@@ -4466,7 +4468,7 @@
         <v>137</v>
       </c>
       <c r="I63" s="14">
-        <v>282</v>
+        <v>127.77</v>
       </c>
       <c r="J63" s="14">
         <v>0</v>
@@ -4477,7 +4479,7 @@
       </c>
       <c r="L63" s="16">
         <f>SUM(I63:K63)</f>
-        <v>282</v>
+        <v>127.77</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="12.75">
@@ -7583,11 +7585,11 @@
       </c>
       <c r="K136" s="16">
         <f>J136*($L$2-1)</f>
-        <v>116.16562999999999</v>
+        <v>124.554644</v>
       </c>
       <c r="L136" s="16">
         <f>SUM(I136:K136)</f>
-        <v>377.50563</v>
+        <v>385.89464400000003</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="12.75">

--- a/GWD Data/GWD MR Abstract.xlsx
+++ b/GWD Data/GWD MR Abstract.xlsx
@@ -1229,7 +1229,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1245,6 +1245,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DD0E1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F7FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1377,7 +1395,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1400,19 +1418,31 @@
     <xf numFmtId="177" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1424,39 +1454,6 @@
     <cellStyle name="Comma" xfId="18" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF4DD0E1"/>
-          <bgColor rgb="FF4DD0E1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="GWD MR Abstract-style" pivot="0" table="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="0"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
-    </tableStyle>
-  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1566,6 +1563,7 @@
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
       <sheetName val="PVC Fittings PRICE"/>
+      <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
       <sheetName val="PVC wo Trench"/>
       <sheetName val="PVC With Trench"/>
@@ -1620,29 +1618,10 @@
       <sheetData sheetId="36"/>
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_2" displayName="Table_2" ref="A3:L197">
-  <tableColumns count="12">
-    <tableColumn id="1" name="Sl No"/>
-    <tableColumn id="2" name="Code"/>
-    <tableColumn id="3" name="Item Name"/>
-    <tableColumn id="4" name="Item Name With Code"/>
-    <tableColumn id="5" name="Unit"/>
-    <tableColumn id="6" name="Main Category"/>
-    <tableColumn id="7" name="Sub Category 1"/>
-    <tableColumn id="8" name="Sub Category 2"/>
-    <tableColumn id="9" name="C1"/>
-    <tableColumn id="10" name="C2"/>
-    <tableColumn id="11" name="Indexed"/>
-    <tableColumn id="12" name="Total"/>
-  </tableColumns>
-  <tableStyleInfo name="GWD MR Abstract-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1941,7 +1920,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B3F80A-05D2-4DB7-9DA1-227D42C7B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D23B45-9E43-4E94-9450-9EBDF4BFB9A6}">
   <dimension ref="A1:L197"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -2064,42 +2043,42 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="12.75">
-      <c r="A5" s="14">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="15" t="str">
+      <c r="D5" s="18" t="str">
         <f>CONCATENATE(C5," (Code: ",B5,")")</f>
         <v>S&amp;F PVC Bend 140 mm (DG) (Code: GWDMR002)</v>
       </c>
-      <c r="E5" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="16" t="s">
+      <c r="E5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="17">
         <v>150</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="17">
         <v>35</v>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="19">
         <f>J5*($L$2-1)</f>
         <v>16.681000000000001</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5" s="19">
         <f>SUM(I5:K5)</f>
         <v>201.68100000000001</v>
       </c>
@@ -2146,42 +2125,42 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="12.75">
-      <c r="A7" s="14">
+      <c r="A7" s="17">
         <v>4</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="15" t="str">
+      <c r="D7" s="18" t="str">
         <f>CONCATENATE(C7," (Code: ",B7,")")</f>
         <v>PVC End cap 150 mm (DG) (Code: GWDMR004)</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="16" t="s">
+      <c r="E7" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="17">
         <v>41.20</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="17">
         <v>39.50</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="19">
         <f>J7*($L$2-1)</f>
         <v>18.825700000000001</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="19">
         <f>SUM(I7:K7)</f>
         <v>99.525700000000001</v>
       </c>
@@ -2228,42 +2207,42 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="12.75">
-      <c r="A9" s="14">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="15" t="str">
+      <c r="D9" s="18" t="str">
         <f>CONCATENATE(C9," (Code: ",B9,")")</f>
         <v>PVC End Cap 200 mm (DG) (Code: GWDMR006)</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="E9" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="17">
         <v>52.50</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="17">
         <v>48.50</v>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="19">
         <f>J9*($L$2-1)</f>
         <v>23.115100000000002</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="19">
         <f>SUM(I9:K9)</f>
         <v>124.1151</v>
       </c>
@@ -2294,7 +2273,7 @@
       <c r="H10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="20">
         <v>200</v>
       </c>
       <c r="J10" s="14">
@@ -2310,42 +2289,42 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="12.75">
-      <c r="A11" s="14">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="15" t="str">
+      <c r="D11" s="18" t="str">
         <f>CONCATENATE(C11," (Code: ",B11,")")</f>
         <v>PVC Square End Cap 160 mm (Code: GWDMR008)</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="16" t="s">
+      <c r="E11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="17">
         <v>250</v>
       </c>
-      <c r="J11" s="14">
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
+      <c r="J11" s="17">
+        <v>0</v>
+      </c>
+      <c r="K11" s="19">
         <f>J11*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="19">
         <f>SUM(I11:K11)</f>
         <v>250</v>
       </c>
@@ -2376,7 +2355,7 @@
       <c r="H12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="20">
         <v>150</v>
       </c>
       <c r="J12" s="14">
@@ -2392,42 +2371,42 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="12.75">
-      <c r="A13" s="14">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="15" t="str">
+      <c r="D13" s="18" t="str">
         <f>CONCATENATE(C13," (Code: ",B13,")")</f>
         <v>PVC Half  End Cap 160 mm (Code: GWDMR010)</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="16" t="s">
+      <c r="E13" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="17">
         <v>160</v>
       </c>
-      <c r="J13" s="14">
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="19">
         <f>J13*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="19">
         <f>SUM(I13:K13)</f>
         <v>160</v>
       </c>
@@ -2458,7 +2437,7 @@
       <c r="H14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="20">
         <v>150</v>
       </c>
       <c r="J14" s="14">
@@ -2474,42 +2453,42 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="12.75">
-      <c r="A15" s="14">
+      <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="15" t="str">
+      <c r="D15" s="18" t="str">
         <f>CONCATENATE(C15," (Code: ",B15,")")</f>
         <v>PVC Half Square End Cap 160 mm (Code: GWDMR012)</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="16" t="s">
+      <c r="E15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="17">
         <v>175</v>
       </c>
-      <c r="J15" s="14">
-        <v>0</v>
-      </c>
-      <c r="K15" s="16">
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="19">
         <f>J15*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="19">
         <f>SUM(I15:K15)</f>
         <v>175</v>
       </c>
@@ -2556,42 +2535,42 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.75">
-      <c r="A17" s="14">
+      <c r="A17" s="17">
         <v>14</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="15" t="str">
+      <c r="D17" s="18" t="str">
         <f>CONCATENATE(C17," (Code: ",B17,")")</f>
         <v>S&amp;F PVC Tee 140 mm (DG) (Code: GWDMR014)</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="16" t="s">
+      <c r="E17" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="17">
         <v>160</v>
       </c>
-      <c r="J17" s="14">
+      <c r="J17" s="17">
         <v>36</v>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="19">
         <f>J17*($L$2-1)</f>
         <v>17.157599999999999</v>
       </c>
-      <c r="L17" s="16">
+      <c r="L17" s="19">
         <f>SUM(I17:K17)</f>
         <v>213.1576</v>
       </c>
@@ -2638,42 +2617,42 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="12.75">
-      <c r="A19" s="14">
+      <c r="A19" s="17">
         <v>16</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="15" t="str">
+      <c r="D19" s="18" t="str">
         <f>CONCATENATE(C19," (Code: ",B19,")")</f>
         <v>PVC Reducer 90X75 mm (Code: GWDMR016)</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="16" t="s">
+      <c r="E19" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="17">
         <v>73</v>
       </c>
-      <c r="J19" s="14">
-        <v>0</v>
-      </c>
-      <c r="K19" s="16">
+      <c r="J19" s="17">
+        <v>0</v>
+      </c>
+      <c r="K19" s="19">
         <f>J19*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="19">
         <f>SUM(I19:K19)</f>
         <v>73</v>
       </c>
@@ -2720,42 +2699,42 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="12.75">
-      <c r="A21" s="14">
-        <v>18</v>
-      </c>
-      <c r="B21" s="15" t="s">
+      <c r="A21" s="17">
+        <v>18</v>
+      </c>
+      <c r="B21" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="15" t="str">
+      <c r="D21" s="18" t="str">
         <f>CONCATENATE(C21," (Code: ",B21,")")</f>
         <v>PVC Reducer 140X90 mm (Code: GWDMR018)</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="16" t="s">
+      <c r="E21" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="17">
         <v>156</v>
       </c>
-      <c r="J21" s="14">
-        <v>0</v>
-      </c>
-      <c r="K21" s="16">
+      <c r="J21" s="17">
+        <v>0</v>
+      </c>
+      <c r="K21" s="19">
         <f>J21*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="19">
         <f>SUM(I21:K21)</f>
         <v>156</v>
       </c>
@@ -2802,42 +2781,42 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.75">
-      <c r="A23" s="14">
+      <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="15" t="str">
+      <c r="D23" s="18" t="str">
         <f>CONCATENATE(C23," (Code: ",B23,")")</f>
         <v>PVC Reducer 160X110 mm (Code: GWDMR020)</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="16" t="s">
+      <c r="E23" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="14">
+      <c r="I23" s="17">
         <v>290</v>
       </c>
-      <c r="J23" s="14">
-        <v>0</v>
-      </c>
-      <c r="K23" s="16">
+      <c r="J23" s="17">
+        <v>0</v>
+      </c>
+      <c r="K23" s="19">
         <f>J23*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="16">
+      <c r="L23" s="19">
         <f>SUM(I23:K23)</f>
         <v>290</v>
       </c>
@@ -2884,42 +2863,42 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.75">
-      <c r="A25" s="14">
+      <c r="A25" s="17">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="15" t="str">
+      <c r="D25" s="18" t="str">
         <f>CONCATENATE(C25," (Code: ",B25,")")</f>
         <v>PVC Runner Drop 140 mm (Code: GWDMR021)</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="16" t="s">
+      <c r="E25" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="17">
         <v>210</v>
       </c>
-      <c r="J25" s="14">
-        <v>0</v>
-      </c>
-      <c r="K25" s="16">
+      <c r="J25" s="17">
+        <v>0</v>
+      </c>
+      <c r="K25" s="19">
         <f>J25*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="16">
+      <c r="L25" s="19">
         <f>SUM(I25:K25)</f>
         <v>210</v>
       </c>
@@ -2966,42 +2945,42 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="12.75">
-      <c r="A27" s="14">
+      <c r="A27" s="17">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="15" t="str">
+      <c r="D27" s="18" t="str">
         <f>CONCATENATE(C27," (Code: ",B27,")")</f>
         <v>PVC  End Drop 140 mm (Code: GWDMR023)</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="16" t="s">
+      <c r="E27" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="17">
         <v>192</v>
       </c>
-      <c r="J27" s="14">
-        <v>0</v>
-      </c>
-      <c r="K27" s="16">
+      <c r="J27" s="17">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
         <f>J27*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="16">
+      <c r="L27" s="19">
         <f>SUM(I27:K27)</f>
         <v>192</v>
       </c>
@@ -3048,42 +3027,42 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="12.75">
-      <c r="A29" s="14">
+      <c r="A29" s="17">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="15" t="str">
+      <c r="D29" s="18" t="str">
         <f>CONCATENATE(C29," (Code: ",B29,")")</f>
         <v>PVC Half End Drop 140 mm (Code: GWDMR025)</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="16" t="s">
+      <c r="E29" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="17">
         <v>174</v>
       </c>
-      <c r="J29" s="14">
-        <v>0</v>
-      </c>
-      <c r="K29" s="16">
+      <c r="J29" s="17">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
         <f>J29*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="16">
+      <c r="L29" s="19">
         <f>SUM(I29:K29)</f>
         <v>174</v>
       </c>
@@ -3130,42 +3109,42 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="12.75">
-      <c r="A31" s="14">
+      <c r="A31" s="17">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="18" t="str">
         <f>CONCATENATE(C31," (Code: ",B31,")")</f>
         <v>PVC Square End Drop 140 mm (Code: GWDMR027)</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="16" t="s">
+      <c r="E31" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="14">
+      <c r="I31" s="17">
         <v>198</v>
       </c>
-      <c r="J31" s="14">
-        <v>0</v>
-      </c>
-      <c r="K31" s="16">
+      <c r="J31" s="17">
+        <v>0</v>
+      </c>
+      <c r="K31" s="19">
         <f>J31*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="16">
+      <c r="L31" s="19">
         <f>SUM(I31:K31)</f>
         <v>198</v>
       </c>
@@ -3212,42 +3191,42 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="12.75">
-      <c r="A33" s="14">
+      <c r="A33" s="17">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="15" t="str">
+      <c r="D33" s="18" t="str">
         <f>CONCATENATE(C33," (Code: ",B33,")")</f>
         <v>PVC Square Half End Drop 140 mm (Code: GWDMR029)</v>
       </c>
-      <c r="E33" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="16" t="s">
+      <c r="E33" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="17">
         <v>180</v>
       </c>
-      <c r="J33" s="14">
-        <v>0</v>
-      </c>
-      <c r="K33" s="16">
+      <c r="J33" s="17">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19">
         <f>J33*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="19">
         <f>SUM(I33:K33)</f>
         <v>180</v>
       </c>
@@ -3294,42 +3273,42 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="12.75">
-      <c r="A35" s="14">
+      <c r="A35" s="17">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="15" t="str">
+      <c r="D35" s="18" t="str">
         <f>CONCATENATE(C35," (Code: ",B35,")")</f>
         <v>S&amp;F PVC 45o Elbow 90 mm (DG) (Code: GWDMR031)</v>
       </c>
-      <c r="E35" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="16" t="s">
+      <c r="E35" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="17">
         <v>45</v>
       </c>
-      <c r="J35" s="14">
+      <c r="J35" s="17">
         <v>31.50</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="19">
         <f>J35*($L$2-1)</f>
         <v>15.0129</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="19">
         <f>SUM(I35:K35)</f>
         <v>91.512900000000002</v>
       </c>
@@ -3376,42 +3355,42 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="12.75">
-      <c r="A37" s="14">
+      <c r="A37" s="17">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="15" t="str">
+      <c r="D37" s="18" t="str">
         <f>CONCATENATE(C37," (Code: ",B37,")")</f>
         <v>S&amp;F PVC 45o Elbow 160 mm (DG) (Code: GWDMR033)</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="16" t="s">
+      <c r="E37" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="17">
         <v>95</v>
       </c>
-      <c r="J37" s="14">
+      <c r="J37" s="17">
         <v>42</v>
       </c>
-      <c r="K37" s="16">
+      <c r="K37" s="19">
         <f>J37*($L$2-1)</f>
         <v>20.017199999999999</v>
       </c>
-      <c r="L37" s="16">
+      <c r="L37" s="19">
         <f>SUM(I37:K37)</f>
         <v>157.0172</v>
       </c>
@@ -3458,42 +3437,42 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="12.75">
-      <c r="A39" s="14">
+      <c r="A39" s="17">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="15" t="str">
+      <c r="D39" s="18" t="str">
         <f>CONCATENATE(C39," (Code: ",B39,")")</f>
         <v>PVC Tank connector 40 mm (Code: GWDMR035)</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H39" s="16" t="s">
+      <c r="E39" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="I39" s="14">
+      <c r="I39" s="17">
         <v>240</v>
       </c>
-      <c r="J39" s="14">
-        <v>0</v>
-      </c>
-      <c r="K39" s="16">
+      <c r="J39" s="17">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19">
         <f>J39*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L39" s="16">
+      <c r="L39" s="19">
         <f>SUM(I39:K39)</f>
         <v>240</v>
       </c>
@@ -3540,42 +3519,42 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="12.75">
-      <c r="A41" s="14">
+      <c r="A41" s="17">
         <v>37</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="15" t="str">
+      <c r="D41" s="18" t="str">
         <f>CONCATENATE(C41," (Code: ",B41,")")</f>
         <v>PVC Tank connector 63 mm (Code: GWDMR037)</v>
       </c>
-      <c r="E41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H41" s="16" t="s">
+      <c r="E41" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="I41" s="14">
+      <c r="I41" s="17">
         <v>420</v>
       </c>
-      <c r="J41" s="14">
-        <v>0</v>
-      </c>
-      <c r="K41" s="16">
+      <c r="J41" s="17">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19">
         <f>J41*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="16">
+      <c r="L41" s="19">
         <f>SUM(I41:K41)</f>
         <v>420</v>
       </c>
@@ -3622,42 +3601,42 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="12.75">
-      <c r="A43" s="14">
+      <c r="A43" s="17">
         <v>39</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="15" t="str">
+      <c r="D43" s="18" t="str">
         <f>CONCATENATE(C43," (Code: ",B43,")")</f>
         <v>PVC Tank connector 90 mm (Code: GWDMR039)</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" s="16" t="s">
+      <c r="E43" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="I43" s="14">
+      <c r="I43" s="17">
         <v>540</v>
       </c>
-      <c r="J43" s="14">
-        <v>0</v>
-      </c>
-      <c r="K43" s="16">
+      <c r="J43" s="17">
+        <v>0</v>
+      </c>
+      <c r="K43" s="19">
         <f>J43*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L43" s="16">
+      <c r="L43" s="19">
         <f>SUM(I43:K43)</f>
         <v>540</v>
       </c>
@@ -3704,42 +3683,42 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="12.75">
-      <c r="A45" s="14">
+      <c r="A45" s="17">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="15" t="str">
+      <c r="D45" s="18" t="str">
         <f>CONCATENATE(C45," (Code: ",B45,")")</f>
         <v>PVC Ball valve 32 mm (Code: GWDMR041)</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" s="16" t="s">
+      <c r="E45" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I45" s="14">
+      <c r="I45" s="17">
         <v>216</v>
       </c>
-      <c r="J45" s="14">
-        <v>0</v>
-      </c>
-      <c r="K45" s="16">
+      <c r="J45" s="17">
+        <v>0</v>
+      </c>
+      <c r="K45" s="19">
         <f>J45*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L45" s="16">
+      <c r="L45" s="19">
         <f>SUM(I45:K45)</f>
         <v>216</v>
       </c>
@@ -3786,42 +3765,42 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="12.75">
-      <c r="A47" s="14">
+      <c r="A47" s="17">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="15" t="str">
+      <c r="D47" s="18" t="str">
         <f>CONCATENATE(C47," (Code: ",B47,")")</f>
         <v>PVC Ball valve 50 mm (Code: GWDMR043)</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H47" s="16" t="s">
+      <c r="E47" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I47" s="14">
+      <c r="I47" s="17">
         <v>456</v>
       </c>
-      <c r="J47" s="14">
-        <v>0</v>
-      </c>
-      <c r="K47" s="16">
+      <c r="J47" s="17">
+        <v>0</v>
+      </c>
+      <c r="K47" s="19">
         <f>J47*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L47" s="16">
+      <c r="L47" s="19">
         <f>SUM(I47:K47)</f>
         <v>456</v>
       </c>
@@ -3868,42 +3847,42 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="12.75">
-      <c r="A49" s="14">
+      <c r="A49" s="17">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="15" t="str">
+      <c r="D49" s="18" t="str">
         <f>CONCATENATE(C49," (Code: ",B49,")")</f>
         <v>PVC Ball valve 75 mm (Code: GWDMR045)</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" s="16" t="s">
+      <c r="E49" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I49" s="14">
+      <c r="I49" s="17">
         <v>720</v>
       </c>
-      <c r="J49" s="14">
-        <v>0</v>
-      </c>
-      <c r="K49" s="16">
+      <c r="J49" s="17">
+        <v>0</v>
+      </c>
+      <c r="K49" s="19">
         <f>J49*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L49" s="16">
+      <c r="L49" s="19">
         <f>SUM(I49:K49)</f>
         <v>720</v>
       </c>
@@ -3950,42 +3929,42 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="12.75">
-      <c r="A51" s="14">
+      <c r="A51" s="17">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="15" t="str">
+      <c r="D51" s="18" t="str">
         <f>CONCATENATE(C51," (Code: ",B51,")")</f>
         <v>PVC Ball valve 110 mm (Code: GWDMR047)</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H51" s="16" t="s">
+      <c r="E51" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="I51" s="14">
+      <c r="I51" s="17">
         <v>1020</v>
       </c>
-      <c r="J51" s="14">
-        <v>0</v>
-      </c>
-      <c r="K51" s="16">
+      <c r="J51" s="17">
+        <v>0</v>
+      </c>
+      <c r="K51" s="19">
         <f>J51*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="16">
+      <c r="L51" s="19">
         <f>SUM(I51:K51)</f>
         <v>1020</v>
       </c>
@@ -4032,42 +4011,42 @@
       </c>
     </row>
     <row r="53" spans="1:12" ht="12.75">
-      <c r="A53" s="14">
+      <c r="A53" s="17">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D53" s="15" t="str">
+      <c r="D53" s="18" t="str">
         <f>CONCATENATE(C53," (Code: ",B53,")")</f>
         <v>S&amp;F PVC Coupling 40 mm (DG) (Code: GWDMR049)</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="16" t="s">
+      <c r="E53" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="I53" s="14">
+      <c r="I53" s="17">
         <v>22.50</v>
       </c>
-      <c r="J53" s="14">
+      <c r="J53" s="17">
         <v>28.46</v>
       </c>
-      <c r="K53" s="16">
+      <c r="K53" s="19">
         <f>J53*($L$2-1)</f>
         <v>13.564036</v>
       </c>
-      <c r="L53" s="16">
+      <c r="L53" s="19">
         <f>SUM(I53:K53)</f>
         <v>64.524035999999995</v>
       </c>
@@ -4114,42 +4093,42 @@
       </c>
     </row>
     <row r="55" spans="1:12" ht="12.75">
-      <c r="A55" s="14">
+      <c r="A55" s="17">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="s">
+      <c r="B55" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="15" t="str">
+      <c r="D55" s="18" t="str">
         <f>CONCATENATE(C55," (Code: ",B55,")")</f>
         <v>S&amp;F PVC Coupling 63 mm (DG) (Code: GWDMR051)</v>
       </c>
-      <c r="E55" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="16" t="s">
+      <c r="E55" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="I55" s="14">
+      <c r="I55" s="17">
         <v>28.46</v>
       </c>
-      <c r="J55" s="14">
+      <c r="J55" s="17">
         <v>29.77</v>
       </c>
-      <c r="K55" s="16">
+      <c r="K55" s="19">
         <f>J55*($L$2-1)</f>
         <v>14.188382000000001</v>
       </c>
-      <c r="L55" s="16">
+      <c r="L55" s="19">
         <f>SUM(I55:K55)</f>
         <v>72.418381999999994</v>
       </c>
@@ -4196,42 +4175,42 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="12.75">
-      <c r="A57" s="14">
+      <c r="A57" s="17">
         <v>53</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="D57" s="15" t="str">
+      <c r="D57" s="18" t="str">
         <f>CONCATENATE(C57," (Code: ",B57,")")</f>
         <v>GI Bend 40 mm (Code: GWDMR053)</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H57" s="16" t="s">
+      <c r="E57" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I57" s="14">
+      <c r="I57" s="17">
         <v>162</v>
       </c>
-      <c r="J57" s="14">
-        <v>0</v>
-      </c>
-      <c r="K57" s="16">
+      <c r="J57" s="17">
+        <v>0</v>
+      </c>
+      <c r="K57" s="19">
         <f>J57*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L57" s="16">
+      <c r="L57" s="19">
         <f>SUM(I57:K57)</f>
         <v>162</v>
       </c>
@@ -4278,42 +4257,42 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="12.75">
-      <c r="A59" s="14">
+      <c r="A59" s="17">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B59" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="15" t="str">
+      <c r="D59" s="18" t="str">
         <f>CONCATENATE(C59," (Code: ",B59,")")</f>
         <v>GI Bend 65 mm (Code: GWDMR055)</v>
       </c>
-      <c r="E59" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H59" s="16" t="s">
+      <c r="E59" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I59" s="14">
+      <c r="I59" s="17">
         <v>414</v>
       </c>
-      <c r="J59" s="14">
-        <v>0</v>
-      </c>
-      <c r="K59" s="16">
+      <c r="J59" s="17">
+        <v>0</v>
+      </c>
+      <c r="K59" s="19">
         <f>J59*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L59" s="16">
+      <c r="L59" s="19">
         <f>SUM(I59:K59)</f>
         <v>414</v>
       </c>
@@ -4360,42 +4339,42 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="12.75">
-      <c r="A61" s="14">
+      <c r="A61" s="17">
         <v>57</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="C61" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="D61" s="15" t="str">
+      <c r="D61" s="18" t="str">
         <f>CONCATENATE(C61," (Code: ",B61,")")</f>
         <v>GI Socket 40 mm (Code: GWDMR057)</v>
       </c>
-      <c r="E61" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" s="16" t="s">
+      <c r="E61" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I61" s="14">
+      <c r="I61" s="17">
         <v>69.69</v>
       </c>
-      <c r="J61" s="14">
-        <v>0</v>
-      </c>
-      <c r="K61" s="16">
+      <c r="J61" s="17">
+        <v>0</v>
+      </c>
+      <c r="K61" s="19">
         <f>J61*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L61" s="16">
+      <c r="L61" s="19">
         <f>SUM(I61:K61)</f>
         <v>69.69</v>
       </c>
@@ -4442,42 +4421,42 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="12.75">
-      <c r="A63" s="14">
+      <c r="A63" s="17">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="s">
+      <c r="B63" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="15" t="s">
+      <c r="C63" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="D63" s="15" t="str">
+      <c r="D63" s="18" t="str">
         <f>CONCATENATE(C63," (Code: ",B63,")")</f>
         <v>GI Socket 65 mm (Code: GWDMR059)</v>
       </c>
-      <c r="E63" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" s="16" t="s">
+      <c r="E63" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H63" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I63" s="14">
+      <c r="I63" s="17">
         <v>127.77</v>
       </c>
-      <c r="J63" s="14">
-        <v>0</v>
-      </c>
-      <c r="K63" s="16">
+      <c r="J63" s="17">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19">
         <f>J63*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L63" s="16">
+      <c r="L63" s="19">
         <f>SUM(I63:K63)</f>
         <v>127.77</v>
       </c>
@@ -4524,42 +4503,42 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="12.75">
-      <c r="A65" s="14">
+      <c r="A65" s="17">
         <v>61</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="C65" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="15" t="str">
+      <c r="D65" s="18" t="str">
         <f>CONCATENATE(C65," (Code: ",B65,")")</f>
         <v>GI Tee 40 mm (Code: GWDMR061)</v>
       </c>
-      <c r="E65" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H65" s="16" t="s">
+      <c r="E65" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H65" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I65" s="14">
+      <c r="I65" s="17">
         <v>270</v>
       </c>
-      <c r="J65" s="14">
-        <v>0</v>
-      </c>
-      <c r="K65" s="16">
+      <c r="J65" s="17">
+        <v>0</v>
+      </c>
+      <c r="K65" s="19">
         <f>J65*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L65" s="16">
+      <c r="L65" s="19">
         <f>SUM(I65:K65)</f>
         <v>270</v>
       </c>
@@ -4606,42 +4585,42 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="12.75">
-      <c r="A67" s="14">
+      <c r="A67" s="17">
         <v>63</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C67" s="15" t="s">
+      <c r="C67" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D67" s="15" t="str">
+      <c r="D67" s="18" t="str">
         <f>CONCATENATE(C67," (Code: ",B67,")")</f>
         <v>GI Tee 65 mm (Code: GWDMR063)</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H67" s="16" t="s">
+      <c r="E67" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H67" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I67" s="14">
+      <c r="I67" s="17">
         <v>636</v>
       </c>
-      <c r="J67" s="14">
-        <v>0</v>
-      </c>
-      <c r="K67" s="16">
+      <c r="J67" s="17">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19">
         <f>J67*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L67" s="16">
+      <c r="L67" s="19">
         <f>SUM(I67:K67)</f>
         <v>636</v>
       </c>
@@ -4673,7 +4652,7 @@
         <v>162</v>
       </c>
       <c r="I68" s="14">
-        <v>22044</v>
+        <v>23970</v>
       </c>
       <c r="J68" s="14">
         <v>0</v>
@@ -4684,48 +4663,48 @@
       </c>
       <c r="L68" s="16">
         <f>SUM(I68:K68)</f>
-        <v>22044</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="12.75">
-      <c r="A69" s="14">
+      <c r="A69" s="17">
         <v>65</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="15" t="s">
+      <c r="C69" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="15" t="str">
+      <c r="D69" s="18" t="str">
         <f>CONCATENATE(C69," (Code: ",B69,")")</f>
         <v>Compressor pump 2 HP single phase (Code: GWDMR065)</v>
       </c>
-      <c r="E69" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H69" s="16" t="s">
+      <c r="E69" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H69" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="I69" s="14">
-        <v>25080</v>
-      </c>
-      <c r="J69" s="14">
-        <v>0</v>
-      </c>
-      <c r="K69" s="16">
+      <c r="I69" s="17">
+        <v>27540</v>
+      </c>
+      <c r="J69" s="17">
+        <v>0</v>
+      </c>
+      <c r="K69" s="19">
         <f>J69*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L69" s="16">
+      <c r="L69" s="19">
         <f>SUM(I69:K69)</f>
-        <v>25080</v>
+        <v>27540</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="12.75">
@@ -4755,7 +4734,7 @@
         <v>162</v>
       </c>
       <c r="I70" s="14">
-        <v>36036</v>
+        <v>38760</v>
       </c>
       <c r="J70" s="14">
         <v>0</v>
@@ -4766,48 +4745,48 @@
       </c>
       <c r="L70" s="16">
         <f>SUM(I70:K70)</f>
-        <v>36036</v>
+        <v>38760</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="12.75">
-      <c r="A71" s="14">
+      <c r="A71" s="17">
         <v>67</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="15" t="s">
+      <c r="C71" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="15" t="str">
+      <c r="D71" s="18" t="str">
         <f>CONCATENATE(C71," (Code: ",B71,")")</f>
         <v>Compressor pump 7.5 HP three phase (Code: GWDMR067)</v>
       </c>
-      <c r="E71" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H71" s="16" t="s">
+      <c r="E71" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="I71" s="14">
-        <v>47652</v>
-      </c>
-      <c r="J71" s="14">
-        <v>0</v>
-      </c>
-      <c r="K71" s="16">
+      <c r="I71" s="17">
+        <v>51000</v>
+      </c>
+      <c r="J71" s="17">
+        <v>0</v>
+      </c>
+      <c r="K71" s="19">
         <f>J71*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L71" s="16">
+      <c r="L71" s="19">
         <f>SUM(I71:K71)</f>
-        <v>47652</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="12.75">
@@ -4852,42 +4831,42 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="12.75">
-      <c r="A73" s="14">
+      <c r="A73" s="17">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C73" s="15" t="s">
+      <c r="C73" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="15" t="str">
+      <c r="D73" s="18" t="str">
         <f>CONCATENATE(C73," (Code: ",B73,")")</f>
         <v>14 mm thick nylon rope (Code: GWDMR069)</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F73" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H73" s="16" t="s">
+      <c r="F73" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H73" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I73" s="14">
+      <c r="I73" s="17">
         <v>49.20</v>
       </c>
-      <c r="J73" s="14">
-        <v>0</v>
-      </c>
-      <c r="K73" s="16">
+      <c r="J73" s="17">
+        <v>0</v>
+      </c>
+      <c r="K73" s="19">
         <f>J73*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L73" s="16">
+      <c r="L73" s="19">
         <f>SUM(I73:K73)</f>
         <v>49.20</v>
       </c>
@@ -4934,42 +4913,42 @@
       </c>
     </row>
     <row r="75" spans="1:12" ht="12.75">
-      <c r="A75" s="14">
+      <c r="A75" s="17">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C75" s="15" t="s">
+      <c r="C75" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D75" s="15" t="str">
+      <c r="D75" s="18" t="str">
         <f>CONCATENATE(C75," (Code: ",B75,")")</f>
         <v>Steel rope (Code: GWDMR071)</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F75" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H75" s="16" t="s">
+      <c r="F75" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H75" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I75" s="14">
+      <c r="I75" s="17">
         <v>114</v>
       </c>
-      <c r="J75" s="14">
-        <v>0</v>
-      </c>
-      <c r="K75" s="16">
+      <c r="J75" s="17">
+        <v>0</v>
+      </c>
+      <c r="K75" s="19">
         <f>J75*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L75" s="16">
+      <c r="L75" s="19">
         <f>SUM(I75:K75)</f>
         <v>114</v>
       </c>
@@ -5016,42 +4995,42 @@
       </c>
     </row>
     <row r="77" spans="1:12" ht="12.75">
-      <c r="A77" s="14">
+      <c r="A77" s="17">
         <v>73</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D77" s="15" t="str">
+      <c r="D77" s="18" t="str">
         <f>CONCATENATE(C77," (Code: ",B77,")")</f>
         <v>40 mm dia UPVC pipe (Code: GWDMR073)</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F77" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H77" s="16" t="s">
+      <c r="F77" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H77" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I77" s="14">
+      <c r="I77" s="17">
         <v>354</v>
       </c>
-      <c r="J77" s="14">
-        <v>0</v>
-      </c>
-      <c r="K77" s="16">
+      <c r="J77" s="17">
+        <v>0</v>
+      </c>
+      <c r="K77" s="19">
         <f>J77*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="16">
+      <c r="L77" s="19">
         <f>SUM(I77:K77)</f>
         <v>354</v>
       </c>
@@ -5098,42 +5077,42 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="12.75">
-      <c r="A79" s="14">
+      <c r="A79" s="17">
         <v>75</v>
       </c>
-      <c r="B79" s="15" t="s">
+      <c r="B79" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="D79" s="15" t="str">
+      <c r="D79" s="18" t="str">
         <f>CONCATENATE(C79," (Code: ",B79,")")</f>
         <v>63 mm dia UPVC pipe (Code: GWDMR075)</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H79" s="16" t="s">
+      <c r="F79" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H79" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I79" s="14">
+      <c r="I79" s="17">
         <v>552</v>
       </c>
-      <c r="J79" s="14">
-        <v>0</v>
-      </c>
-      <c r="K79" s="16">
+      <c r="J79" s="17">
+        <v>0</v>
+      </c>
+      <c r="K79" s="19">
         <f>J79*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L79" s="16">
+      <c r="L79" s="19">
         <f>SUM(I79:K79)</f>
         <v>552</v>
       </c>
@@ -5180,42 +5159,42 @@
       </c>
     </row>
     <row r="81" spans="1:12" ht="12.75">
-      <c r="A81" s="14">
+      <c r="A81" s="17">
         <v>77</v>
       </c>
-      <c r="B81" s="15" t="s">
+      <c r="B81" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D81" s="15" t="str">
+      <c r="D81" s="18" t="str">
         <f>CONCATENATE(C81," (Code: ",B81,")")</f>
         <v>32 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR077)</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F81" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H81" s="16" t="s">
+      <c r="F81" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I81" s="14">
+      <c r="I81" s="17">
         <v>35</v>
       </c>
-      <c r="J81" s="14">
-        <v>0</v>
-      </c>
-      <c r="K81" s="16">
+      <c r="J81" s="17">
+        <v>0</v>
+      </c>
+      <c r="K81" s="19">
         <f>J81*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L81" s="16">
+      <c r="L81" s="19">
         <f>SUM(I81:K81)</f>
         <v>35</v>
       </c>
@@ -5262,42 +5241,42 @@
       </c>
     </row>
     <row r="83" spans="1:12" ht="12.75">
-      <c r="A83" s="14">
+      <c r="A83" s="17">
         <v>79</v>
       </c>
-      <c r="B83" s="15" t="s">
+      <c r="B83" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C83" s="15" t="s">
+      <c r="C83" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="D83" s="15" t="str">
+      <c r="D83" s="18" t="str">
         <f>CONCATENATE(C83," (Code: ",B83,")")</f>
         <v>32 mm SS Adapter (Code: GWDMR079)</v>
       </c>
-      <c r="E83" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H83" s="16" t="s">
+      <c r="E83" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H83" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I83" s="14">
+      <c r="I83" s="17">
         <v>804</v>
       </c>
-      <c r="J83" s="14">
-        <v>0</v>
-      </c>
-      <c r="K83" s="16">
+      <c r="J83" s="17">
+        <v>0</v>
+      </c>
+      <c r="K83" s="19">
         <f>J83*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L83" s="16">
+      <c r="L83" s="19">
         <f>SUM(I83:K83)</f>
         <v>804</v>
       </c>
@@ -5344,42 +5323,42 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="12.75">
-      <c r="A85" s="14">
+      <c r="A85" s="17">
         <v>81</v>
       </c>
-      <c r="B85" s="15" t="s">
+      <c r="B85" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="C85" s="15" t="s">
+      <c r="C85" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="D85" s="15" t="str">
+      <c r="D85" s="18" t="str">
         <f>CONCATENATE(C85," (Code: ",B85,")")</f>
         <v>50 mm SS Adapter (Code: GWDMR081)</v>
       </c>
-      <c r="E85" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H85" s="16" t="s">
+      <c r="E85" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H85" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I85" s="14">
+      <c r="I85" s="17">
         <v>1200</v>
       </c>
-      <c r="J85" s="14">
-        <v>0</v>
-      </c>
-      <c r="K85" s="16">
+      <c r="J85" s="17">
+        <v>0</v>
+      </c>
+      <c r="K85" s="19">
         <f>J85*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L85" s="16">
+      <c r="L85" s="19">
         <f>SUM(I85:K85)</f>
         <v>1200</v>
       </c>
@@ -5426,42 +5405,42 @@
       </c>
     </row>
     <row r="87" spans="1:12" ht="12.75">
-      <c r="A87" s="14">
+      <c r="A87" s="17">
         <v>83</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="D87" s="15" t="str">
+      <c r="D87" s="18" t="str">
         <f>CONCATENATE(C87," (Code: ",B87,")")</f>
         <v>63 mm UPVC Union (Code: GWDMR083)</v>
       </c>
-      <c r="E87" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H87" s="16" t="s">
+      <c r="E87" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H87" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="I87" s="14">
+      <c r="I87" s="17">
         <v>540</v>
       </c>
-      <c r="J87" s="14">
-        <v>0</v>
-      </c>
-      <c r="K87" s="16">
+      <c r="J87" s="17">
+        <v>0</v>
+      </c>
+      <c r="K87" s="19">
         <f>J87*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L87" s="16">
+      <c r="L87" s="19">
         <f>SUM(I87:K87)</f>
         <v>540</v>
       </c>
@@ -5508,42 +5487,42 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="12.75">
-      <c r="A89" s="14">
+      <c r="A89" s="17">
         <v>85</v>
       </c>
-      <c r="B89" s="15" t="s">
+      <c r="B89" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="D89" s="15" t="str">
+      <c r="D89" s="18" t="str">
         <f>CONCATENATE(C89," (Code: ",B89,")")</f>
         <v>Sodium Bentonite (ordinary) (Code: GWDMR085)</v>
       </c>
-      <c r="E89" s="14" t="s">
+      <c r="E89" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G89" s="16" t="s">
+      <c r="F89" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="H89" s="16" t="s">
+      <c r="H89" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="I89" s="14">
+      <c r="I89" s="17">
         <v>7000</v>
       </c>
-      <c r="J89" s="14">
-        <v>0</v>
-      </c>
-      <c r="K89" s="16">
+      <c r="J89" s="17">
+        <v>0</v>
+      </c>
+      <c r="K89" s="19">
         <f>J89*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L89" s="16">
+      <c r="L89" s="19">
         <f>SUM(I89:K89)</f>
         <v>7000</v>
       </c>
@@ -5590,42 +5569,42 @@
       </c>
     </row>
     <row r="91" spans="1:12" ht="12.75">
-      <c r="A91" s="14">
+      <c r="A91" s="17">
         <v>87</v>
       </c>
-      <c r="B91" s="15" t="s">
+      <c r="B91" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="C91" s="15" t="s">
+      <c r="C91" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D91" s="15" t="str">
+      <c r="D91" s="18" t="str">
         <f>CONCATENATE(C91," (Code: ",B91,")")</f>
         <v>MS Casing pipe 450 mm dia, 6 mm thickness (Code: GWDMR087)</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="E91" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F91" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="16" t="s">
+      <c r="F91" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="H91" s="16" t="s">
+      <c r="H91" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="I91" s="14">
+      <c r="I91" s="17">
         <v>8450</v>
       </c>
-      <c r="J91" s="14">
-        <v>0</v>
-      </c>
-      <c r="K91" s="16">
+      <c r="J91" s="17">
+        <v>0</v>
+      </c>
+      <c r="K91" s="19">
         <f>J91*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L91" s="16">
+      <c r="L91" s="19">
         <f>SUM(I91:K91)</f>
         <v>8450</v>
       </c>
@@ -5656,7 +5635,7 @@
       <c r="H92" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I92" s="14">
+      <c r="I92" s="20">
         <v>180</v>
       </c>
       <c r="J92" s="14">
@@ -5672,42 +5651,42 @@
       </c>
     </row>
     <row r="93" spans="1:12" ht="12.75">
-      <c r="A93" s="14">
+      <c r="A93" s="17">
         <v>89</v>
       </c>
-      <c r="B93" s="15" t="s">
+      <c r="B93" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C93" s="15" t="s">
+      <c r="C93" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="D93" s="15" t="str">
+      <c r="D93" s="18" t="str">
         <f>CONCATENATE(C93," (Code: ",B93,")")</f>
         <v>Coated mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR089)</v>
       </c>
-      <c r="E93" s="14" t="s">
+      <c r="E93" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="F93" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G93" s="16" t="s">
+      <c r="F93" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H93" s="16" t="s">
+      <c r="H93" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I93" s="14">
+      <c r="I93" s="17">
         <v>300</v>
       </c>
-      <c r="J93" s="14">
-        <v>0</v>
-      </c>
-      <c r="K93" s="16">
+      <c r="J93" s="17">
+        <v>0</v>
+      </c>
+      <c r="K93" s="19">
         <f>J93*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L93" s="16">
+      <c r="L93" s="19">
         <f>SUM(I93:K93)</f>
         <v>300</v>
       </c>
@@ -5738,7 +5717,7 @@
       <c r="H94" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I94" s="14">
+      <c r="I94" s="20">
         <v>180</v>
       </c>
       <c r="J94" s="14">
@@ -5754,42 +5733,42 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="12.75">
-      <c r="A95" s="14">
+      <c r="A95" s="17">
         <v>91</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C95" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="D95" s="15" t="str">
+      <c r="D95" s="18" t="str">
         <f>CONCATENATE(C95," (Code: ",B95,")")</f>
         <v>Sieve mesh 140 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR091)</v>
       </c>
-      <c r="E95" s="14" t="s">
+      <c r="E95" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="F95" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G95" s="16" t="s">
+      <c r="F95" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="H95" s="16" t="s">
+      <c r="H95" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I95" s="14">
+      <c r="I95" s="17">
         <v>200</v>
       </c>
-      <c r="J95" s="14">
-        <v>0</v>
-      </c>
-      <c r="K95" s="16">
+      <c r="J95" s="17">
+        <v>0</v>
+      </c>
+      <c r="K95" s="19">
         <f>J95*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L95" s="16">
+      <c r="L95" s="19">
         <f>SUM(I95:K95)</f>
         <v>200</v>
       </c>
@@ -5820,7 +5799,7 @@
       <c r="H96" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I96" s="14">
+      <c r="I96" s="20">
         <v>50</v>
       </c>
       <c r="J96" s="14">
@@ -5836,42 +5815,42 @@
       </c>
     </row>
     <row r="97" spans="1:12" ht="12.75">
-      <c r="A97" s="14">
+      <c r="A97" s="17">
         <v>93</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="C97" s="15" t="s">
+      <c r="C97" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D97" s="15" t="str">
+      <c r="D97" s="18" t="str">
         <f>CONCATENATE(C97," (Code: ",B97,")")</f>
         <v>PVC Wiring Pipe (Code: GWDMR093)</v>
       </c>
-      <c r="E97" s="14" t="s">
+      <c r="E97" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="F97" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H97" s="16" t="s">
+      <c r="F97" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H97" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="I97" s="14">
+      <c r="I97" s="17">
         <v>30</v>
       </c>
-      <c r="J97" s="14">
-        <v>0</v>
-      </c>
-      <c r="K97" s="16">
+      <c r="J97" s="17">
+        <v>0</v>
+      </c>
+      <c r="K97" s="19">
         <f>J97*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L97" s="16">
+      <c r="L97" s="19">
         <f>SUM(I97:K97)</f>
         <v>30</v>
       </c>
@@ -5921,45 +5900,45 @@
       </c>
     </row>
     <row r="99" spans="1:12" ht="12.75">
-      <c r="A99" s="14">
+      <c r="A99" s="17">
         <v>95</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="C99" s="15" t="str">
+      <c r="C99" s="18" t="str">
         <f>'[1]HP Repair Spares'!E2</f>
         <v>Head with welded components only without cover</v>
       </c>
-      <c r="D99" s="15" t="str">
+      <c r="D99" s="18" t="str">
         <f>CONCATENATE(C99," (Code: ",B99,")")</f>
         <v>Head with welded components only without cover (Code: GWDMR095)</v>
       </c>
-      <c r="E99" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" s="16" t="s">
+      <c r="E99" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H99" s="16" t="s">
+      <c r="H99" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I99" s="14">
+      <c r="I99" s="17">
         <f>'[1]HP Repair Spares'!F2</f>
         <v>2280</v>
       </c>
-      <c r="J99" s="14">
+      <c r="J99" s="17">
         <f>'[1]HP Repair Spares'!G2</f>
         <v>0</v>
       </c>
-      <c r="K99" s="16">
+      <c r="K99" s="19">
         <f>J99*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L99" s="16">
+      <c r="L99" s="19">
         <f>SUM(I99:K99)</f>
         <v>2280</v>
       </c>
@@ -6009,45 +5988,45 @@
       </c>
     </row>
     <row r="101" spans="1:12" ht="12.75">
-      <c r="A101" s="14">
-        <v>97</v>
-      </c>
-      <c r="B101" s="15" t="s">
+      <c r="A101" s="17">
+        <v>97</v>
+      </c>
+      <c r="B101" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="C101" s="15" t="str">
+      <c r="C101" s="18" t="str">
         <f>'[1]HP Repair Spares'!E4</f>
         <v>Additional Plate</v>
       </c>
-      <c r="D101" s="15" t="str">
+      <c r="D101" s="18" t="str">
         <f>CONCATENATE(C101," (Code: ",B101,")")</f>
         <v>Additional Plate (Code: GWDMR097)</v>
       </c>
-      <c r="E101" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" s="16" t="s">
+      <c r="E101" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H101" s="16" t="s">
+      <c r="H101" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I101" s="14">
+      <c r="I101" s="17">
         <f>'[1]HP Repair Spares'!F4</f>
         <v>450</v>
       </c>
-      <c r="J101" s="14">
+      <c r="J101" s="17">
         <f>'[1]HP Repair Spares'!G4</f>
         <v>0</v>
       </c>
-      <c r="K101" s="16">
+      <c r="K101" s="19">
         <f>J101*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L101" s="16">
+      <c r="L101" s="19">
         <f>SUM(I101:K101)</f>
         <v>450</v>
       </c>
@@ -6097,45 +6076,45 @@
       </c>
     </row>
     <row r="103" spans="1:12" ht="12.75">
-      <c r="A103" s="14">
+      <c r="A103" s="17">
         <v>99</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C103" s="15" t="str">
+      <c r="C103" s="18" t="str">
         <f>'[1]HP Repair Spares'!E6</f>
         <v>Chain with coupling</v>
       </c>
-      <c r="D103" s="15" t="str">
+      <c r="D103" s="18" t="str">
         <f>CONCATENATE(C103," (Code: ",B103,")")</f>
         <v>Chain with coupling (Code: GWDMR099)</v>
       </c>
-      <c r="E103" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F103" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G103" s="16" t="s">
+      <c r="E103" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H103" s="16" t="s">
+      <c r="H103" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I103" s="14">
+      <c r="I103" s="17">
         <f>'[1]HP Repair Spares'!F6</f>
         <v>240</v>
       </c>
-      <c r="J103" s="14">
+      <c r="J103" s="17">
         <f>'[1]HP Repair Spares'!G6</f>
         <v>0</v>
       </c>
-      <c r="K103" s="16">
+      <c r="K103" s="19">
         <f>J103*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="16">
+      <c r="L103" s="19">
         <f>SUM(I103:K103)</f>
         <v>240</v>
       </c>
@@ -6185,45 +6164,45 @@
       </c>
     </row>
     <row r="105" spans="1:12" ht="12.75">
-      <c r="A105" s="14">
+      <c r="A105" s="17">
         <v>101</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="C105" s="15" t="str">
+      <c r="C105" s="18" t="str">
         <f>'[1]HP Repair Spares'!E8</f>
         <v>M 12 x 20 Hex Bolt for Top Head Cover</v>
       </c>
-      <c r="D105" s="15" t="str">
+      <c r="D105" s="18" t="str">
         <f>CONCATENATE(C105," (Code: ",B105,")")</f>
         <v>M 12 x 20 Hex Bolt for Top Head Cover (Code: GWDMR101)</v>
       </c>
-      <c r="E105" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F105" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" s="16" t="s">
+      <c r="E105" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H105" s="16" t="s">
+      <c r="H105" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I105" s="14">
+      <c r="I105" s="17">
         <f>'[1]HP Repair Spares'!F8</f>
         <v>18</v>
       </c>
-      <c r="J105" s="14">
+      <c r="J105" s="17">
         <f>'[1]HP Repair Spares'!G8</f>
         <v>0</v>
       </c>
-      <c r="K105" s="16">
+      <c r="K105" s="19">
         <f>J105*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L105" s="16">
+      <c r="L105" s="19">
         <f>SUM(I105:K105)</f>
         <v>18</v>
       </c>
@@ -6273,45 +6252,45 @@
       </c>
     </row>
     <row r="107" spans="1:12" ht="12.75">
-      <c r="A107" s="14">
+      <c r="A107" s="17">
         <v>103</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="C107" s="15" t="str">
+      <c r="C107" s="18" t="str">
         <f>'[1]HP Repair Spares'!E10</f>
         <v>M 12 Nut</v>
       </c>
-      <c r="D107" s="15" t="str">
+      <c r="D107" s="18" t="str">
         <f>CONCATENATE(C107," (Code: ",B107,")")</f>
         <v>M 12 Nut (Code: GWDMR103)</v>
       </c>
-      <c r="E107" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G107" s="16" t="s">
+      <c r="E107" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H107" s="16" t="s">
+      <c r="H107" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I107" s="14">
+      <c r="I107" s="17">
         <f>'[1]HP Repair Spares'!F10</f>
         <v>12</v>
       </c>
-      <c r="J107" s="14">
+      <c r="J107" s="17">
         <f>'[1]HP Repair Spares'!G10</f>
         <v>0</v>
       </c>
-      <c r="K107" s="16">
+      <c r="K107" s="19">
         <f>J107*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L107" s="16">
+      <c r="L107" s="19">
         <f>SUM(I107:K107)</f>
         <v>12</v>
       </c>
@@ -6361,45 +6340,45 @@
       </c>
     </row>
     <row r="109" spans="1:12" ht="12.75">
-      <c r="A109" s="14">
+      <c r="A109" s="17">
         <v>105</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="C109" s="15" t="str">
+      <c r="C109" s="18" t="str">
         <f>'[1]HP Repair Spares'!E12</f>
         <v>M 10 x 40 H.T Bolt</v>
       </c>
-      <c r="D109" s="15" t="str">
+      <c r="D109" s="18" t="str">
         <f>CONCATENATE(C109," (Code: ",B109,")")</f>
         <v>M 10 x 40 H.T Bolt (Code: GWDMR105)</v>
       </c>
-      <c r="E109" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F109" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G109" s="16" t="s">
+      <c r="E109" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H109" s="16" t="s">
+      <c r="H109" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I109" s="14">
+      <c r="I109" s="17">
         <f>'[1]HP Repair Spares'!F12</f>
         <v>18</v>
       </c>
-      <c r="J109" s="14">
+      <c r="J109" s="17">
         <f>'[1]HP Repair Spares'!G12</f>
         <v>0</v>
       </c>
-      <c r="K109" s="16">
+      <c r="K109" s="19">
         <f>J109*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L109" s="16">
+      <c r="L109" s="19">
         <f>SUM(I109:K109)</f>
         <v>18</v>
       </c>
@@ -6449,45 +6428,45 @@
       </c>
     </row>
     <row r="111" spans="1:12" ht="12.75">
-      <c r="A111" s="14">
+      <c r="A111" s="17">
         <v>107</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C111" s="15" t="str">
+      <c r="C111" s="18" t="str">
         <f>'[1]HP Repair Spares'!E14</f>
         <v>Special Washer for Axle</v>
       </c>
-      <c r="D111" s="15" t="str">
+      <c r="D111" s="18" t="str">
         <f>CONCATENATE(C111," (Code: ",B111,")")</f>
         <v>Special Washer for Axle (Code: GWDMR107)</v>
       </c>
-      <c r="E111" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F111" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G111" s="16" t="s">
+      <c r="E111" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H111" s="16" t="s">
+      <c r="H111" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I111" s="14">
+      <c r="I111" s="17">
         <f>'[1]HP Repair Spares'!F14</f>
         <v>12</v>
       </c>
-      <c r="J111" s="14">
+      <c r="J111" s="17">
         <f>'[1]HP Repair Spares'!G14</f>
         <v>0</v>
       </c>
-      <c r="K111" s="16">
+      <c r="K111" s="19">
         <f>J111*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L111" s="16">
+      <c r="L111" s="19">
         <f>SUM(I111:K111)</f>
         <v>12</v>
       </c>
@@ -6537,45 +6516,45 @@
       </c>
     </row>
     <row r="113" spans="1:12" ht="12.75">
-      <c r="A113" s="14">
+      <c r="A113" s="17">
         <v>109</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="C113" s="15" t="str">
+      <c r="C113" s="18" t="str">
         <f>'[1]HP Repair Spares'!E16</f>
         <v>C.I.Cylinder Body with liner</v>
       </c>
-      <c r="D113" s="15" t="str">
+      <c r="D113" s="18" t="str">
         <f>CONCATENATE(C113," (Code: ",B113,")")</f>
         <v>C.I.Cylinder Body with liner (Code: GWDMR109)</v>
       </c>
-      <c r="E113" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F113" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G113" s="16" t="s">
+      <c r="E113" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H113" s="16" t="s">
+      <c r="H113" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I113" s="14">
+      <c r="I113" s="17">
         <f>'[1]HP Repair Spares'!F16</f>
         <v>1080</v>
       </c>
-      <c r="J113" s="14">
+      <c r="J113" s="17">
         <f>'[1]HP Repair Spares'!G16</f>
         <v>0</v>
       </c>
-      <c r="K113" s="16">
+      <c r="K113" s="19">
         <f>J113*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L113" s="16">
+      <c r="L113" s="19">
         <f>SUM(I113:K113)</f>
         <v>1080</v>
       </c>
@@ -6625,45 +6604,45 @@
       </c>
     </row>
     <row r="115" spans="1:12" ht="12.75">
-      <c r="A115" s="14">
+      <c r="A115" s="17">
         <v>111</v>
       </c>
-      <c r="B115" s="15" t="s">
+      <c r="B115" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="C115" s="15" t="str">
+      <c r="C115" s="18" t="str">
         <f>'[1]HP Repair Spares'!E18</f>
         <v>Reducer cap</v>
       </c>
-      <c r="D115" s="15" t="str">
+      <c r="D115" s="18" t="str">
         <f>CONCATENATE(C115," (Code: ",B115,")")</f>
         <v>Reducer cap (Code: GWDMR111)</v>
       </c>
-      <c r="E115" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G115" s="16" t="s">
+      <c r="E115" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H115" s="16" t="s">
+      <c r="H115" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I115" s="14">
+      <c r="I115" s="17">
         <f>'[1]HP Repair Spares'!F18</f>
         <v>156</v>
       </c>
-      <c r="J115" s="14">
+      <c r="J115" s="17">
         <f>'[1]HP Repair Spares'!G18</f>
         <v>0</v>
       </c>
-      <c r="K115" s="16">
+      <c r="K115" s="19">
         <f>J115*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L115" s="16">
+      <c r="L115" s="19">
         <f>SUM(I115:K115)</f>
         <v>156</v>
       </c>
@@ -6713,45 +6692,45 @@
       </c>
     </row>
     <row r="117" spans="1:12" ht="12.75">
-      <c r="A117" s="14">
+      <c r="A117" s="17">
         <v>113</v>
       </c>
-      <c r="B117" s="15" t="s">
+      <c r="B117" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="C117" s="15" t="str">
+      <c r="C117" s="18" t="str">
         <f>'[1]HP Repair Spares'!E20</f>
         <v>Spacer</v>
       </c>
-      <c r="D117" s="15" t="str">
+      <c r="D117" s="18" t="str">
         <f>CONCATENATE(C117," (Code: ",B117,")")</f>
         <v>Spacer (Code: GWDMR113)</v>
       </c>
-      <c r="E117" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F117" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G117" s="16" t="s">
+      <c r="E117" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H117" s="16" t="s">
+      <c r="H117" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I117" s="14">
+      <c r="I117" s="17">
         <f>'[1]HP Repair Spares'!F20</f>
         <v>228</v>
       </c>
-      <c r="J117" s="14">
+      <c r="J117" s="17">
         <f>'[1]HP Repair Spares'!G20</f>
         <v>0</v>
       </c>
-      <c r="K117" s="16">
+      <c r="K117" s="19">
         <f>J117*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L117" s="16">
+      <c r="L117" s="19">
         <f>SUM(I117:K117)</f>
         <v>228</v>
       </c>
@@ -6801,45 +6780,45 @@
       </c>
     </row>
     <row r="119" spans="1:12" ht="12.75">
-      <c r="A119" s="14">
+      <c r="A119" s="17">
         <v>115</v>
       </c>
-      <c r="B119" s="15" t="s">
+      <c r="B119" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="C119" s="15" t="str">
+      <c r="C119" s="18" t="str">
         <f>'[1]HP Repair Spares'!E22</f>
         <v>Upper Valve ( one piece)</v>
       </c>
-      <c r="D119" s="15" t="str">
+      <c r="D119" s="18" t="str">
         <f>CONCATENATE(C119," (Code: ",B119,")")</f>
         <v>Upper Valve ( one piece) (Code: GWDMR115)</v>
       </c>
-      <c r="E119" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F119" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G119" s="16" t="s">
+      <c r="E119" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H119" s="16" t="s">
+      <c r="H119" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I119" s="14">
+      <c r="I119" s="17">
         <f>'[1]HP Repair Spares'!F22</f>
         <v>90</v>
       </c>
-      <c r="J119" s="14">
+      <c r="J119" s="17">
         <f>'[1]HP Repair Spares'!G22</f>
         <v>0</v>
       </c>
-      <c r="K119" s="16">
+      <c r="K119" s="19">
         <f>J119*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L119" s="16">
+      <c r="L119" s="19">
         <f>SUM(I119:K119)</f>
         <v>90</v>
       </c>
@@ -6889,45 +6868,45 @@
       </c>
     </row>
     <row r="121" spans="1:12" ht="12.75">
-      <c r="A121" s="14">
+      <c r="A121" s="17">
         <v>117</v>
       </c>
-      <c r="B121" s="15" t="s">
+      <c r="B121" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C121" s="15" t="str">
+      <c r="C121" s="18" t="str">
         <f>'[1]HP Repair Spares'!E24</f>
         <v>Check valve seat</v>
       </c>
-      <c r="D121" s="15" t="str">
+      <c r="D121" s="18" t="str">
         <f>CONCATENATE(C121," (Code: ",B121,")")</f>
         <v>Check valve seat (Code: GWDMR117)</v>
       </c>
-      <c r="E121" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F121" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G121" s="16" t="s">
+      <c r="E121" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H121" s="16" t="s">
+      <c r="H121" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I121" s="14">
+      <c r="I121" s="17">
         <f>'[1]HP Repair Spares'!F24</f>
         <v>192</v>
       </c>
-      <c r="J121" s="14">
+      <c r="J121" s="17">
         <f>'[1]HP Repair Spares'!G24</f>
         <v>0</v>
       </c>
-      <c r="K121" s="16">
+      <c r="K121" s="19">
         <f>J121*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L121" s="16">
+      <c r="L121" s="19">
         <f>SUM(I121:K121)</f>
         <v>192</v>
       </c>
@@ -6977,45 +6956,45 @@
       </c>
     </row>
     <row r="123" spans="1:12" ht="12.75">
-      <c r="A123" s="14">
+      <c r="A123" s="17">
         <v>119</v>
       </c>
-      <c r="B123" s="15" t="s">
+      <c r="B123" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="C123" s="15" t="str">
+      <c r="C123" s="18" t="str">
         <f>'[1]HP Repair Spares'!E26</f>
         <v>Sealing ring (Nitrile Rubber)</v>
       </c>
-      <c r="D123" s="15" t="str">
+      <c r="D123" s="18" t="str">
         <f>CONCATENATE(C123," (Code: ",B123,")")</f>
         <v>Sealing ring (Nitrile Rubber) (Code: GWDMR119)</v>
       </c>
-      <c r="E123" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F123" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G123" s="16" t="s">
+      <c r="E123" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H123" s="16" t="s">
+      <c r="H123" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I123" s="14">
+      <c r="I123" s="17">
         <f>'[1]HP Repair Spares'!F26</f>
         <v>18</v>
       </c>
-      <c r="J123" s="14">
+      <c r="J123" s="17">
         <f>'[1]HP Repair Spares'!G26</f>
         <v>0</v>
       </c>
-      <c r="K123" s="16">
+      <c r="K123" s="19">
         <f>J123*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L123" s="16">
+      <c r="L123" s="19">
         <f>SUM(I123:K123)</f>
         <v>18</v>
       </c>
@@ -7065,45 +7044,45 @@
       </c>
     </row>
     <row r="125" spans="1:12" ht="12.75">
-      <c r="A125" s="14">
+      <c r="A125" s="17">
         <v>121</v>
       </c>
-      <c r="B125" s="15" t="s">
+      <c r="B125" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="C125" s="15" t="str">
+      <c r="C125" s="18" t="str">
         <f>'[1]HP Repair Spares'!E28</f>
         <v>Rubber seating check valve</v>
       </c>
-      <c r="D125" s="15" t="str">
+      <c r="D125" s="18" t="str">
         <f>CONCATENATE(C125," (Code: ",B125,")")</f>
         <v>Rubber seating check valve (Code: GWDMR121)</v>
       </c>
-      <c r="E125" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G125" s="16" t="s">
+      <c r="E125" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H125" s="16" t="s">
+      <c r="H125" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I125" s="14">
+      <c r="I125" s="17">
         <f>'[1]HP Repair Spares'!F28</f>
         <v>12</v>
       </c>
-      <c r="J125" s="14">
+      <c r="J125" s="17">
         <f>'[1]HP Repair Spares'!G28</f>
         <v>0</v>
       </c>
-      <c r="K125" s="16">
+      <c r="K125" s="19">
         <f>J125*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L125" s="16">
+      <c r="L125" s="19">
         <f>SUM(I125:K125)</f>
         <v>12</v>
       </c>
@@ -7153,45 +7132,45 @@
       </c>
     </row>
     <row r="127" spans="1:12" ht="12.75">
-      <c r="A127" s="14">
+      <c r="A127" s="17">
         <v>123</v>
       </c>
-      <c r="B127" s="15" t="s">
+      <c r="B127" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="15" t="str">
+      <c r="C127" s="18" t="str">
         <f>'[1]HP Repair Spares'!E30</f>
         <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers</v>
       </c>
-      <c r="D127" s="15" t="str">
+      <c r="D127" s="18" t="str">
         <f>CONCATENATE(C127," (Code: ",B127,")")</f>
         <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers (Code: GWDMR123)</v>
       </c>
-      <c r="E127" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" s="16" t="s">
+      <c r="E127" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H127" s="16" t="s">
+      <c r="H127" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I127" s="14">
+      <c r="I127" s="17">
         <f>'[1]HP Repair Spares'!F30</f>
         <v>1200</v>
       </c>
-      <c r="J127" s="14">
+      <c r="J127" s="17">
         <f>'[1]HP Repair Spares'!G30</f>
         <v>0</v>
       </c>
-      <c r="K127" s="16">
+      <c r="K127" s="19">
         <f>J127*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L127" s="16">
+      <c r="L127" s="19">
         <f>SUM(I127:K127)</f>
         <v>1200</v>
       </c>
@@ -7241,45 +7220,45 @@
       </c>
     </row>
     <row r="129" spans="1:12" ht="12.75">
-      <c r="A129" s="14">
+      <c r="A129" s="17">
         <v>125</v>
       </c>
-      <c r="B129" s="15" t="s">
+      <c r="B129" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C129" s="15" t="str">
+      <c r="C129" s="18" t="str">
         <f>'[1]HP Repair Spares'!E32</f>
         <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating</v>
       </c>
-      <c r="D129" s="15" t="str">
+      <c r="D129" s="18" t="str">
         <f>CONCATENATE(C129," (Code: ",B129,")")</f>
         <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating (Code: GWDMR125)</v>
       </c>
-      <c r="E129" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="16" t="s">
+      <c r="E129" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F129" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H129" s="16" t="s">
+      <c r="H129" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I129" s="14">
+      <c r="I129" s="17">
         <f>'[1]HP Repair Spares'!F32</f>
         <v>540</v>
       </c>
-      <c r="J129" s="14">
+      <c r="J129" s="17">
         <f>'[1]HP Repair Spares'!G32</f>
         <v>0</v>
       </c>
-      <c r="K129" s="16">
+      <c r="K129" s="19">
         <f>J129*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L129" s="16">
+      <c r="L129" s="19">
         <f>SUM(I129:K129)</f>
         <v>540</v>
       </c>
@@ -7329,45 +7308,45 @@
       </c>
     </row>
     <row r="131" spans="1:12" ht="12.75">
-      <c r="A131" s="14">
+      <c r="A131" s="17">
         <v>127</v>
       </c>
-      <c r="B131" s="15" t="s">
+      <c r="B131" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="C131" s="15" t="str">
+      <c r="C131" s="18" t="str">
         <f>'[1]HP Repair Spares'!E34</f>
         <v>Pipe Sockets</v>
       </c>
-      <c r="D131" s="15" t="str">
+      <c r="D131" s="18" t="str">
         <f>CONCATENATE(C131," (Code: ",B131,")")</f>
         <v>Pipe Sockets (Code: GWDMR127)</v>
       </c>
-      <c r="E131" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F131" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" s="16" t="s">
+      <c r="E131" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H131" s="16" t="s">
+      <c r="H131" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I131" s="14">
+      <c r="I131" s="17">
         <f>'[1]HP Repair Spares'!F34</f>
         <v>120</v>
       </c>
-      <c r="J131" s="14">
+      <c r="J131" s="17">
         <f>'[1]HP Repair Spares'!G34</f>
         <v>0</v>
       </c>
-      <c r="K131" s="16">
+      <c r="K131" s="19">
         <f>J131*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L131" s="16">
+      <c r="L131" s="19">
         <f>SUM(I131:K131)</f>
         <v>120</v>
       </c>
@@ -7417,45 +7396,45 @@
       </c>
     </row>
     <row r="133" spans="1:12" ht="12.75">
-      <c r="A133" s="14">
+      <c r="A133" s="17">
         <v>129</v>
       </c>
-      <c r="B133" s="15" t="s">
+      <c r="B133" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="15" t="str">
+      <c r="C133" s="18" t="str">
         <f>'[1]HP Repair Spares'!E36</f>
         <v>12 mm dia x 3 m electro galvanized</v>
       </c>
-      <c r="D133" s="15" t="str">
+      <c r="D133" s="18" t="str">
         <f>CONCATENATE(C133," (Code: ",B133,")")</f>
         <v>12 mm dia x 3 m electro galvanized (Code: GWDMR129)</v>
       </c>
-      <c r="E133" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G133" s="16" t="s">
+      <c r="E133" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H133" s="16" t="s">
+      <c r="H133" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I133" s="14">
+      <c r="I133" s="17">
         <f>'[1]HP Repair Spares'!F36</f>
         <v>336</v>
       </c>
-      <c r="J133" s="14">
+      <c r="J133" s="17">
         <f>'[1]HP Repair Spares'!G36</f>
         <v>0</v>
       </c>
-      <c r="K133" s="16">
+      <c r="K133" s="19">
         <f>J133*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L133" s="16">
+      <c r="L133" s="19">
         <f>SUM(I133:K133)</f>
         <v>336</v>
       </c>
@@ -7505,45 +7484,45 @@
       </c>
     </row>
     <row r="135" spans="1:12" ht="12.75">
-      <c r="A135" s="14">
+      <c r="A135" s="17">
         <v>131</v>
       </c>
-      <c r="B135" s="15" t="s">
+      <c r="B135" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="15" t="str">
+      <c r="C135" s="18" t="str">
         <f>'[1]HP Repair Spares'!E38</f>
         <v>Hex. Coupler 12 x 20 mm</v>
       </c>
-      <c r="D135" s="15" t="str">
+      <c r="D135" s="18" t="str">
         <f>CONCATENATE(C135," (Code: ",B135,")")</f>
         <v>Hex. Coupler 12 x 20 mm (Code: GWDMR131)</v>
       </c>
-      <c r="E135" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F135" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="16" t="s">
+      <c r="E135" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H135" s="16" t="s">
+      <c r="H135" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I135" s="14">
+      <c r="I135" s="17">
         <f>'[1]HP Repair Spares'!F38</f>
         <v>24</v>
       </c>
-      <c r="J135" s="14">
+      <c r="J135" s="17">
         <f>'[1]HP Repair Spares'!G38</f>
         <v>0</v>
       </c>
-      <c r="K135" s="16">
+      <c r="K135" s="19">
         <f>J135*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L135" s="16">
+      <c r="L135" s="19">
         <f>SUM(I135:K135)</f>
         <v>24</v>
       </c>
@@ -7593,45 +7572,45 @@
       </c>
     </row>
     <row r="137" spans="1:12" ht="12.75">
-      <c r="A137" s="14">
+      <c r="A137" s="17">
         <v>133</v>
       </c>
-      <c r="B137" s="15" t="s">
+      <c r="B137" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C137" s="15" t="str">
+      <c r="C137" s="18" t="str">
         <f>'[1]HP Repair Spares'!E40</f>
         <v>Cylinder Extra deep well hand pump</v>
       </c>
-      <c r="D137" s="15" t="str">
+      <c r="D137" s="18" t="str">
         <f>CONCATENATE(C137," (Code: ",B137,")")</f>
         <v>Cylinder Extra deep well hand pump (Code: GWDMR133)</v>
       </c>
-      <c r="E137" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F137" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G137" s="16" t="s">
+      <c r="E137" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H137" s="16" t="s">
+      <c r="H137" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I137" s="14">
+      <c r="I137" s="17">
         <f>'[1]HP Repair Spares'!F40</f>
         <v>4320</v>
       </c>
-      <c r="J137" s="14">
+      <c r="J137" s="17">
         <f>'[1]HP Repair Spares'!G40</f>
         <v>0</v>
       </c>
-      <c r="K137" s="16">
+      <c r="K137" s="19">
         <f>J137*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L137" s="16">
+      <c r="L137" s="19">
         <f>SUM(I137:K137)</f>
         <v>4320</v>
       </c>
@@ -7681,45 +7660,45 @@
       </c>
     </row>
     <row r="139" spans="1:12" ht="12.75">
-      <c r="A139" s="14">
+      <c r="A139" s="17">
         <v>135</v>
       </c>
-      <c r="B139" s="15" t="s">
+      <c r="B139" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="C139" s="15" t="str">
+      <c r="C139" s="18" t="str">
         <f>'[1]HP Repair Spares'!E42</f>
         <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods</v>
       </c>
-      <c r="D139" s="15" t="str">
+      <c r="D139" s="18" t="str">
         <f>CONCATENATE(C139," (Code: ",B139,")")</f>
         <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods (Code: GWDMR135)</v>
       </c>
-      <c r="E139" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G139" s="16" t="s">
+      <c r="E139" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F139" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="H139" s="16" t="s">
+      <c r="H139" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="I139" s="14">
+      <c r="I139" s="17">
         <f>'[1]HP Repair Spares'!F42</f>
         <v>31000</v>
       </c>
-      <c r="J139" s="14">
+      <c r="J139" s="17">
         <f>'[1]HP Repair Spares'!G42</f>
         <v>0</v>
       </c>
-      <c r="K139" s="16">
+      <c r="K139" s="19">
         <f>J139*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L139" s="16">
+      <c r="L139" s="19">
         <f>SUM(I139:K139)</f>
         <v>31000</v>
       </c>
@@ -7769,42 +7748,42 @@
       </c>
     </row>
     <row r="141" spans="1:12" ht="12.75">
-      <c r="A141" s="14">
+      <c r="A141" s="17">
         <v>137</v>
       </c>
-      <c r="B141" s="15" t="s">
+      <c r="B141" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C141" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="D141" s="15" t="str">
+      <c r="D141" s="18" t="str">
         <f>CONCATENATE(C141," (Code: ",B141,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 49-17m without Panel Board (Code: GWDMR137)</v>
       </c>
-      <c r="E141" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F141" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G141" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H141" s="16" t="s">
+      <c r="E141" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G141" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I141" s="16">
+      <c r="I141" s="19">
         <v>21162.53</v>
       </c>
-      <c r="J141" s="14">
-        <v>0</v>
-      </c>
-      <c r="K141" s="16">
+      <c r="J141" s="17">
+        <v>0</v>
+      </c>
+      <c r="K141" s="19">
         <f>J141*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L141" s="16">
+      <c r="L141" s="19">
         <f>SUM(I141:K141)</f>
         <v>21162.53</v>
       </c>
@@ -7851,42 +7830,42 @@
       </c>
     </row>
     <row r="143" spans="1:12" ht="12.75">
-      <c r="A143" s="14">
+      <c r="A143" s="17">
         <v>139</v>
       </c>
-      <c r="B143" s="15" t="s">
+      <c r="B143" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="C143" s="15" t="s">
+      <c r="C143" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="D143" s="15" t="str">
+      <c r="D143" s="18" t="str">
         <f>CONCATENATE(C143," (Code: ",B143,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1800-4320 lph, Head 65-39m without Panel Board (Code: GWDMR139)</v>
       </c>
-      <c r="E143" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F143" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G143" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H143" s="16" t="s">
+      <c r="E143" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F143" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G143" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H143" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I143" s="16">
+      <c r="I143" s="19">
         <v>21047.772000000001</v>
       </c>
-      <c r="J143" s="14">
-        <v>0</v>
-      </c>
-      <c r="K143" s="16">
+      <c r="J143" s="17">
+        <v>0</v>
+      </c>
+      <c r="K143" s="19">
         <f>J143*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L143" s="16">
+      <c r="L143" s="19">
         <f>SUM(I143:K143)</f>
         <v>21047.772000000001</v>
       </c>
@@ -7933,42 +7912,42 @@
       </c>
     </row>
     <row r="145" spans="1:12" ht="12.75">
-      <c r="A145" s="14">
+      <c r="A145" s="17">
         <v>141</v>
       </c>
-      <c r="B145" s="15" t="s">
+      <c r="B145" s="18" t="s">
         <v>282</v>
       </c>
-      <c r="C145" s="15" t="s">
+      <c r="C145" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="D145" s="15" t="str">
+      <c r="D145" s="18" t="str">
         <f>CONCATENATE(C145," (Code: ",B145,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1080-2880 lph, Head 91-50m without Panel Board (Code: GWDMR141)</v>
       </c>
-      <c r="E145" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F145" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G145" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H145" s="16" t="s">
+      <c r="E145" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F145" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H145" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I145" s="16">
+      <c r="I145" s="19">
         <v>22498.716</v>
       </c>
-      <c r="J145" s="14">
-        <v>0</v>
-      </c>
-      <c r="K145" s="16">
+      <c r="J145" s="17">
+        <v>0</v>
+      </c>
+      <c r="K145" s="19">
         <f>J145*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L145" s="16">
+      <c r="L145" s="19">
         <f>SUM(I145:K145)</f>
         <v>22498.716</v>
       </c>
@@ -8015,42 +7994,42 @@
       </c>
     </row>
     <row r="147" spans="1:12" ht="12.75">
-      <c r="A147" s="14">
+      <c r="A147" s="17">
         <v>143</v>
       </c>
-      <c r="B147" s="15" t="s">
+      <c r="B147" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="C147" s="15" t="s">
+      <c r="C147" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D147" s="15" t="str">
+      <c r="D147" s="18" t="str">
         <f>CONCATENATE(C147," (Code: ",B147,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 83-52m without Panel Board (Code: GWDMR143)</v>
       </c>
-      <c r="E147" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F147" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G147" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H147" s="16" t="s">
+      <c r="E147" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G147" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H147" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I147" s="16">
+      <c r="I147" s="19">
         <v>23219.315999999999</v>
       </c>
-      <c r="J147" s="14">
-        <v>0</v>
-      </c>
-      <c r="K147" s="16">
+      <c r="J147" s="17">
+        <v>0</v>
+      </c>
+      <c r="K147" s="19">
         <f>J147*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L147" s="16">
+      <c r="L147" s="19">
         <f>SUM(I147:K147)</f>
         <v>23219.315999999999</v>
       </c>
@@ -8097,42 +8076,42 @@
       </c>
     </row>
     <row r="149" spans="1:12" ht="12.75">
-      <c r="A149" s="14">
+      <c r="A149" s="17">
         <v>145</v>
       </c>
-      <c r="B149" s="15" t="s">
+      <c r="B149" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="C149" s="15" t="s">
+      <c r="C149" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="D149" s="15" t="str">
+      <c r="D149" s="18" t="str">
         <f>CONCATENATE(C149," (Code: ",B149,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 126-43m without Panel Board (Code: GWDMR145)</v>
       </c>
-      <c r="E149" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F149" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G149" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H149" s="16" t="s">
+      <c r="E149" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F149" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G149" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H149" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I149" s="16">
+      <c r="I149" s="19">
         <v>24159.199999999997</v>
       </c>
-      <c r="J149" s="14">
-        <v>0</v>
-      </c>
-      <c r="K149" s="16">
+      <c r="J149" s="17">
+        <v>0</v>
+      </c>
+      <c r="K149" s="19">
         <f>J149*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L149" s="16">
+      <c r="L149" s="19">
         <f>SUM(I149:K149)</f>
         <v>24159.20</v>
       </c>
@@ -8179,42 +8158,42 @@
       </c>
     </row>
     <row r="151" spans="1:12" ht="12.75">
-      <c r="A151" s="14">
+      <c r="A151" s="17">
         <v>147</v>
       </c>
-      <c r="B151" s="15" t="s">
+      <c r="B151" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="C151" s="15" t="s">
+      <c r="C151" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="D151" s="15" t="str">
+      <c r="D151" s="18" t="str">
         <f>CONCATENATE(C151," (Code: ",B151,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 148-50m without Panel Board (Code: GWDMR147)</v>
       </c>
-      <c r="E151" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F151" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G151" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H151" s="16" t="s">
+      <c r="E151" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F151" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H151" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I151" s="16">
+      <c r="I151" s="19">
         <v>27980.534999999996</v>
       </c>
-      <c r="J151" s="14">
-        <v>0</v>
-      </c>
-      <c r="K151" s="16">
+      <c r="J151" s="17">
+        <v>0</v>
+      </c>
+      <c r="K151" s="19">
         <f>J151*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L151" s="16">
+      <c r="L151" s="19">
         <f>SUM(I151:K151)</f>
         <v>27980.535</v>
       </c>
@@ -8261,42 +8240,42 @@
       </c>
     </row>
     <row r="153" spans="1:12" ht="12.75">
-      <c r="A153" s="14">
+      <c r="A153" s="17">
         <v>149</v>
       </c>
-      <c r="B153" s="15" t="s">
+      <c r="B153" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="C153" s="15" t="s">
+      <c r="C153" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="D153" s="15" t="str">
+      <c r="D153" s="18" t="str">
         <f>CONCATENATE(C153," (Code: ",B153,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 5200-10600 lph, Head 57-18m without Panel Board (Code: GWDMR149)</v>
       </c>
-      <c r="E153" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F153" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G153" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H153" s="16" t="s">
+      <c r="E153" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H153" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I153" s="16">
+      <c r="I153" s="19">
         <v>29176.879999999997</v>
       </c>
-      <c r="J153" s="14">
-        <v>0</v>
-      </c>
-      <c r="K153" s="16">
+      <c r="J153" s="17">
+        <v>0</v>
+      </c>
+      <c r="K153" s="19">
         <f>J153*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L153" s="16">
+      <c r="L153" s="19">
         <f>SUM(I153:K153)</f>
         <v>29176.88</v>
       </c>
@@ -8343,42 +8322,42 @@
       </c>
     </row>
     <row r="155" spans="1:12" ht="12.75">
-      <c r="A155" s="14">
+      <c r="A155" s="17">
         <v>151</v>
       </c>
-      <c r="B155" s="15" t="s">
+      <c r="B155" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="C155" s="15" t="s">
+      <c r="C155" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="D155" s="15" t="str">
+      <c r="D155" s="18" t="str">
         <f>CONCATENATE(C155," (Code: ",B155,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 2100-5400 lph, Head 116-33m without Panel Board (Code: GWDMR151)</v>
       </c>
-      <c r="E155" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F155" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G155" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H155" s="16" t="s">
+      <c r="E155" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F155" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H155" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I155" s="16">
+      <c r="I155" s="19">
         <v>29037.499999999996</v>
       </c>
-      <c r="J155" s="14">
-        <v>0</v>
-      </c>
-      <c r="K155" s="16">
+      <c r="J155" s="17">
+        <v>0</v>
+      </c>
+      <c r="K155" s="19">
         <f>J155*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L155" s="16">
+      <c r="L155" s="19">
         <f>SUM(I155:K155)</f>
         <v>29037.50</v>
       </c>
@@ -8425,42 +8404,42 @@
       </c>
     </row>
     <row r="157" spans="1:12" ht="12.75">
-      <c r="A157" s="14">
+      <c r="A157" s="17">
         <v>153</v>
       </c>
-      <c r="B157" s="15" t="s">
+      <c r="B157" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="C157" s="15" t="s">
+      <c r="C157" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="D157" s="15" t="str">
+      <c r="D157" s="18" t="str">
         <f>CONCATENATE(C157," (Code: ",B157,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-3000 lph, Head 194-65m without Panel Board (Code: GWDMR153)</v>
       </c>
-      <c r="E157" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F157" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G157" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H157" s="16" t="s">
+      <c r="E157" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F157" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H157" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I157" s="16">
+      <c r="I157" s="19">
         <v>37864.90</v>
       </c>
-      <c r="J157" s="14">
-        <v>0</v>
-      </c>
-      <c r="K157" s="16">
+      <c r="J157" s="17">
+        <v>0</v>
+      </c>
+      <c r="K157" s="19">
         <f>J157*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L157" s="16">
+      <c r="L157" s="19">
         <f>SUM(I157:K157)</f>
         <v>37864.90</v>
       </c>
@@ -8507,42 +8486,42 @@
       </c>
     </row>
     <row r="159" spans="1:12" ht="12.75">
-      <c r="A159" s="14">
+      <c r="A159" s="17">
         <v>155</v>
       </c>
-      <c r="B159" s="15" t="s">
+      <c r="B159" s="18" t="s">
         <v>310</v>
       </c>
-      <c r="C159" s="15" t="s">
+      <c r="C159" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="D159" s="15" t="str">
+      <c r="D159" s="18" t="str">
         <f>CONCATENATE(C159," (Code: ",B159,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 247-104m without Panel Board (Code: GWDMR155)</v>
       </c>
-      <c r="E159" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G159" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H159" s="16" t="s">
+      <c r="E159" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F159" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H159" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I159" s="16">
+      <c r="I159" s="19">
         <v>47333.447999999997</v>
       </c>
-      <c r="J159" s="14">
-        <v>0</v>
-      </c>
-      <c r="K159" s="16">
+      <c r="J159" s="17">
+        <v>0</v>
+      </c>
+      <c r="K159" s="19">
         <f>J159*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L159" s="16">
+      <c r="L159" s="19">
         <f>SUM(I159:K159)</f>
         <v>47333.447999999997</v>
       </c>
@@ -8589,42 +8568,42 @@
       </c>
     </row>
     <row r="161" spans="1:12" ht="12.75">
-      <c r="A161" s="14">
+      <c r="A161" s="17">
         <v>157</v>
       </c>
-      <c r="B161" s="15" t="s">
+      <c r="B161" s="18" t="s">
         <v>314</v>
       </c>
-      <c r="C161" s="15" t="s">
+      <c r="C161" s="18" t="s">
         <v>315</v>
       </c>
-      <c r="D161" s="15" t="str">
+      <c r="D161" s="18" t="str">
         <f>CONCATENATE(C161," (Code: ",B161,")")</f>
         <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 3240-7200 lph, Head 110-42m without Panel Board (Code: GWDMR157)</v>
       </c>
-      <c r="E161" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F161" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G161" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H161" s="16" t="s">
+      <c r="E161" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F161" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H161" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I161" s="16">
+      <c r="I161" s="19">
         <v>37138.962500000001</v>
       </c>
-      <c r="J161" s="14">
-        <v>0</v>
-      </c>
-      <c r="K161" s="16">
+      <c r="J161" s="17">
+        <v>0</v>
+      </c>
+      <c r="K161" s="19">
         <f>J161*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L161" s="16">
+      <c r="L161" s="19">
         <f>SUM(I161:K161)</f>
         <v>37138.962500000001</v>
       </c>
@@ -8671,42 +8650,42 @@
       </c>
     </row>
     <row r="163" spans="1:12" ht="12.75">
-      <c r="A163" s="14">
+      <c r="A163" s="17">
         <v>159</v>
       </c>
-      <c r="B163" s="15" t="s">
+      <c r="B163" s="18" t="s">
         <v>318</v>
       </c>
-      <c r="C163" s="15" t="s">
+      <c r="C163" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="D163" s="15" t="str">
+      <c r="D163" s="18" t="str">
         <f>CONCATENATE(C163," (Code: ",B163,")")</f>
         <v>Supply of Single Phase Submersible Pump 5 HP, Discharge 4320-10080 lph, Head 150-82m without Panel Board (Code: GWDMR159)</v>
       </c>
-      <c r="E163" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F163" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G163" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H163" s="16" t="s">
+      <c r="E163" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G163" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H163" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I163" s="16">
+      <c r="I163" s="19">
         <v>45301.984499999999</v>
       </c>
-      <c r="J163" s="14">
-        <v>0</v>
-      </c>
-      <c r="K163" s="16">
+      <c r="J163" s="17">
+        <v>0</v>
+      </c>
+      <c r="K163" s="19">
         <f>J163*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L163" s="16">
+      <c r="L163" s="19">
         <f>SUM(I163:K163)</f>
         <v>45301.984499999999</v>
       </c>
@@ -8753,42 +8732,42 @@
       </c>
     </row>
     <row r="165" spans="1:12" ht="12.75">
-      <c r="A165" s="14">
+      <c r="A165" s="17">
         <v>161</v>
       </c>
-      <c r="B165" s="15" t="s">
+      <c r="B165" s="18" t="s">
         <v>322</v>
       </c>
-      <c r="C165" s="15" t="s">
+      <c r="C165" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="D165" s="15" t="str">
+      <c r="D165" s="18" t="str">
         <f>CONCATENATE(C165," (Code: ",B165,")")</f>
         <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 6000-18000 lph, Head 146-90m without Panel Board (Code: GWDMR161)</v>
       </c>
-      <c r="E165" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F165" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G165" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H165" s="16" t="s">
+      <c r="E165" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F165" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G165" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H165" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I165" s="16">
+      <c r="I165" s="19">
         <v>74549.715999999986</v>
       </c>
-      <c r="J165" s="14">
-        <v>0</v>
-      </c>
-      <c r="K165" s="16">
+      <c r="J165" s="17">
+        <v>0</v>
+      </c>
+      <c r="K165" s="19">
         <f>J165*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L165" s="16">
+      <c r="L165" s="19">
         <f>SUM(I165:K165)</f>
         <v>74549.716</v>
       </c>
@@ -8835,42 +8814,42 @@
       </c>
     </row>
     <row r="167" spans="1:12" ht="12.75">
-      <c r="A167" s="14">
+      <c r="A167" s="17">
         <v>163</v>
       </c>
-      <c r="B167" s="15" t="s">
+      <c r="B167" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="C167" s="15" t="s">
+      <c r="C167" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="D167" s="15" t="str">
+      <c r="D167" s="18" t="str">
         <f>CONCATENATE(C167," (Code: ",B167,")")</f>
         <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 5000-14000 lph, Head 205-110m without Panel Board (Code: GWDMR163)</v>
       </c>
-      <c r="E167" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F167" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G167" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H167" s="16" t="s">
+      <c r="E167" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F167" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H167" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I167" s="16">
+      <c r="I167" s="19">
         <v>93543.725499999986</v>
       </c>
-      <c r="J167" s="14">
-        <v>0</v>
-      </c>
-      <c r="K167" s="16">
+      <c r="J167" s="17">
+        <v>0</v>
+      </c>
+      <c r="K167" s="19">
         <f>J167*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L167" s="16">
+      <c r="L167" s="19">
         <f>SUM(I167:K167)</f>
         <v>93543.7255</v>
       </c>
@@ -8917,42 +8896,42 @@
       </c>
     </row>
     <row r="169" spans="1:12" ht="12.75">
-      <c r="A169" s="14">
+      <c r="A169" s="17">
         <v>165</v>
       </c>
-      <c r="B169" s="15" t="s">
+      <c r="B169" s="18" t="s">
         <v>330</v>
       </c>
-      <c r="C169" s="15" t="s">
+      <c r="C169" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D169" s="15" t="str">
+      <c r="D169" s="18" t="str">
         <f>CONCATENATE(C169," (Code: ",B169,")")</f>
         <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3600-25200 lph, Head 157-41m without Panel Board (Code: GWDMR165)</v>
       </c>
-      <c r="E169" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F169" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G169" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H169" s="16" t="s">
+      <c r="E169" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F169" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G169" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H169" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I169" s="16">
+      <c r="I169" s="19">
         <v>77646.274999999994</v>
       </c>
-      <c r="J169" s="14">
-        <v>0</v>
-      </c>
-      <c r="K169" s="16">
+      <c r="J169" s="17">
+        <v>0</v>
+      </c>
+      <c r="K169" s="19">
         <f>J169*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L169" s="16">
+      <c r="L169" s="19">
         <f>SUM(I169:K169)</f>
         <v>77646.274999999994</v>
       </c>
@@ -8999,42 +8978,42 @@
       </c>
     </row>
     <row r="171" spans="1:12" ht="12.75">
-      <c r="A171" s="14">
+      <c r="A171" s="17">
         <v>167</v>
       </c>
-      <c r="B171" s="15" t="s">
+      <c r="B171" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="C171" s="15" t="s">
+      <c r="C171" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="D171" s="15" t="str">
+      <c r="D171" s="18" t="str">
         <f>CONCATENATE(C171," (Code: ",B171,")")</f>
         <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 5000-14000 lph, Head 242-129m without Panel Board (Code: GWDMR167)</v>
       </c>
-      <c r="E171" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G171" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H171" s="16" t="s">
+      <c r="E171" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F171" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H171" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I171" s="16">
+      <c r="I171" s="19">
         <v>103464.09699999999</v>
       </c>
-      <c r="J171" s="14">
-        <v>0</v>
-      </c>
-      <c r="K171" s="16">
+      <c r="J171" s="17">
+        <v>0</v>
+      </c>
+      <c r="K171" s="19">
         <f>J171*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L171" s="16">
+      <c r="L171" s="19">
         <f>SUM(I171:K171)</f>
         <v>103464.09699999999</v>
       </c>
@@ -9081,42 +9060,42 @@
       </c>
     </row>
     <row r="173" spans="1:12" ht="12.75">
-      <c r="A173" s="14">
+      <c r="A173" s="17">
         <v>169</v>
       </c>
-      <c r="B173" s="15" t="s">
+      <c r="B173" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="C173" s="15" t="s">
+      <c r="C173" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="D173" s="15" t="str">
+      <c r="D173" s="18" t="str">
         <f>CONCATENATE(C173," (Code: ",B173,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 5200-10600 lph, Head 86-27m without Panel Board (Code: GWDMR169)</v>
       </c>
-      <c r="E173" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G173" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H173" s="16" t="s">
+      <c r="E173" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F173" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G173" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H173" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I173" s="16">
+      <c r="I173" s="19">
         <v>33242.13</v>
       </c>
-      <c r="J173" s="14">
-        <v>0</v>
-      </c>
-      <c r="K173" s="16">
+      <c r="J173" s="17">
+        <v>0</v>
+      </c>
+      <c r="K173" s="19">
         <f>J173*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L173" s="16">
+      <c r="L173" s="19">
         <f>SUM(I173:K173)</f>
         <v>33242.13</v>
       </c>
@@ -9163,42 +9142,42 @@
       </c>
     </row>
     <row r="175" spans="1:12" ht="12.75">
-      <c r="A175" s="14">
+      <c r="A175" s="17">
         <v>171</v>
       </c>
-      <c r="B175" s="15" t="s">
+      <c r="B175" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="C175" s="15" t="s">
+      <c r="C175" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="D175" s="15" t="str">
+      <c r="D175" s="18" t="str">
         <f>CONCATENATE(C175," (Code: ",B175,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 2500-6000 lph, Head 147-51m without Panel Board (Code: GWDMR171)</v>
       </c>
-      <c r="E175" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F175" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G175" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H175" s="16" t="s">
+      <c r="E175" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F175" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H175" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I175" s="16">
+      <c r="I175" s="19">
         <v>40652.50</v>
       </c>
-      <c r="J175" s="14">
-        <v>0</v>
-      </c>
-      <c r="K175" s="16">
+      <c r="J175" s="17">
+        <v>0</v>
+      </c>
+      <c r="K175" s="19">
         <f>J175*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L175" s="16">
+      <c r="L175" s="19">
         <f>SUM(I175:K175)</f>
         <v>40652.50</v>
       </c>
@@ -9245,42 +9224,42 @@
       </c>
     </row>
     <row r="177" spans="1:12" ht="12.75">
-      <c r="A177" s="14">
+      <c r="A177" s="17">
         <v>173</v>
       </c>
-      <c r="B177" s="15" t="s">
+      <c r="B177" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="C177" s="15" t="s">
+      <c r="C177" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="D177" s="15" t="str">
+      <c r="D177" s="18" t="str">
         <f>CONCATENATE(C177," (Code: ",B177,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 184-86m without Panel Board (Code: GWDMR173)</v>
       </c>
-      <c r="E177" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G177" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H177" s="16" t="s">
+      <c r="E177" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F177" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G177" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H177" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I177" s="16">
+      <c r="I177" s="19">
         <v>38391.059499999996</v>
       </c>
-      <c r="J177" s="14">
-        <v>0</v>
-      </c>
-      <c r="K177" s="16">
+      <c r="J177" s="17">
+        <v>0</v>
+      </c>
+      <c r="K177" s="19">
         <f>J177*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L177" s="16">
+      <c r="L177" s="19">
         <f>SUM(I177:K177)</f>
         <v>38391.059500000003</v>
       </c>
@@ -9327,42 +9306,42 @@
       </c>
     </row>
     <row r="179" spans="1:12" ht="12.75">
-      <c r="A179" s="14">
+      <c r="A179" s="17">
         <v>175</v>
       </c>
-      <c r="B179" s="15" t="s">
+      <c r="B179" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="C179" s="15" t="s">
+      <c r="C179" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="D179" s="15" t="str">
+      <c r="D179" s="18" t="str">
         <f>CONCATENATE(C179," (Code: ",B179,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 245-98m without Panel Board (Code: GWDMR175)</v>
       </c>
-      <c r="E179" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F179" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G179" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H179" s="16" t="s">
+      <c r="E179" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F179" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G179" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H179" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I179" s="16">
+      <c r="I179" s="19">
         <v>53114.233500000002</v>
       </c>
-      <c r="J179" s="14">
-        <v>0</v>
-      </c>
-      <c r="K179" s="16">
+      <c r="J179" s="17">
+        <v>0</v>
+      </c>
+      <c r="K179" s="19">
         <f>J179*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L179" s="16">
+      <c r="L179" s="19">
         <f>SUM(I179:K179)</f>
         <v>53114.233500000002</v>
       </c>
@@ -9409,42 +9388,42 @@
       </c>
     </row>
     <row r="181" spans="1:12" ht="12.75">
-      <c r="A181" s="14">
+      <c r="A181" s="17">
         <v>177</v>
       </c>
-      <c r="B181" s="15" t="s">
+      <c r="B181" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="C181" s="15" t="s">
+      <c r="C181" s="18" t="s">
         <v>355</v>
       </c>
-      <c r="D181" s="15" t="str">
+      <c r="D181" s="18" t="str">
         <f>CONCATENATE(C181," (Code: ",B181,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 7200-15000 lph, Head 78-41m without Panel Board (Code: GWDMR177)</v>
       </c>
-      <c r="E181" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F181" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G181" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H181" s="16" t="s">
+      <c r="E181" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F181" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H181" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I181" s="16">
+      <c r="I181" s="19">
         <v>55751.999999999993</v>
       </c>
-      <c r="J181" s="14">
-        <v>0</v>
-      </c>
-      <c r="K181" s="16">
+      <c r="J181" s="17">
+        <v>0</v>
+      </c>
+      <c r="K181" s="19">
         <f>J181*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L181" s="16">
+      <c r="L181" s="19">
         <f>SUM(I181:K181)</f>
         <v>55752</v>
       </c>
@@ -9491,42 +9470,42 @@
       </c>
     </row>
     <row r="183" spans="1:12" ht="12.75">
-      <c r="A183" s="14">
+      <c r="A183" s="17">
         <v>179</v>
       </c>
-      <c r="B183" s="15" t="s">
+      <c r="B183" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="C183" s="15" t="s">
+      <c r="C183" s="18" t="s">
         <v>359</v>
       </c>
-      <c r="D183" s="15" t="str">
+      <c r="D183" s="18" t="str">
         <f>CONCATENATE(C183," (Code: ",B183,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 102-55m without Panel Board (Code: GWDMR179)</v>
       </c>
-      <c r="E183" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G183" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H183" s="16" t="s">
+      <c r="E183" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F183" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H183" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I183" s="16">
+      <c r="I183" s="19">
         <v>63505.01249999999</v>
       </c>
-      <c r="J183" s="14">
-        <v>0</v>
-      </c>
-      <c r="K183" s="16">
+      <c r="J183" s="17">
+        <v>0</v>
+      </c>
+      <c r="K183" s="19">
         <f>J183*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L183" s="16">
+      <c r="L183" s="19">
         <f>SUM(I183:K183)</f>
         <v>63505.012499999997</v>
       </c>
@@ -9573,42 +9552,42 @@
       </c>
     </row>
     <row r="185" spans="1:12" ht="12.75">
-      <c r="A185" s="14">
+      <c r="A185" s="17">
         <v>181</v>
       </c>
-      <c r="B185" s="15" t="s">
+      <c r="B185" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="C185" s="15" t="s">
+      <c r="C185" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="D185" s="15" t="str">
+      <c r="D185" s="18" t="str">
         <f>CONCATENATE(C185," (Code: ",B185,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3000-9000 lph, Head 140-72m without Panel Board (Code: GWDMR181)</v>
       </c>
-      <c r="E185" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F185" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G185" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H185" s="16" t="s">
+      <c r="E185" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F185" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H185" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I185" s="16">
+      <c r="I185" s="19">
         <v>65052.130499999999</v>
       </c>
-      <c r="J185" s="14">
-        <v>0</v>
-      </c>
-      <c r="K185" s="16">
+      <c r="J185" s="17">
+        <v>0</v>
+      </c>
+      <c r="K185" s="19">
         <f>J185*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L185" s="16">
+      <c r="L185" s="19">
         <f>SUM(I185:K185)</f>
         <v>65052.130499999999</v>
       </c>
@@ -9655,42 +9634,42 @@
       </c>
     </row>
     <row r="187" spans="1:12" ht="12.75">
-      <c r="A187" s="14">
+      <c r="A187" s="17">
         <v>183</v>
       </c>
-      <c r="B187" s="15" t="s">
+      <c r="B187" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="C187" s="15" t="s">
+      <c r="C187" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="D187" s="15" t="str">
+      <c r="D187" s="18" t="str">
         <f>CONCATENATE(C187," (Code: ",B187,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2000-6000 lph, Head 195-120m without Panel Board (Code: GWDMR183)</v>
       </c>
-      <c r="E187" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F187" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G187" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H187" s="16" t="s">
+      <c r="E187" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F187" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G187" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H187" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I187" s="16">
+      <c r="I187" s="19">
         <v>56820.579999999994</v>
       </c>
-      <c r="J187" s="14">
-        <v>0</v>
-      </c>
-      <c r="K187" s="16">
+      <c r="J187" s="17">
+        <v>0</v>
+      </c>
+      <c r="K187" s="19">
         <f>J187*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L187" s="16">
+      <c r="L187" s="19">
         <f>SUM(I187:K187)</f>
         <v>56820.58</v>
       </c>
@@ -9737,42 +9716,42 @@
       </c>
     </row>
     <row r="189" spans="1:12" ht="12.75">
-      <c r="A189" s="14">
+      <c r="A189" s="17">
         <v>185</v>
       </c>
-      <c r="B189" s="15" t="s">
+      <c r="B189" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="C189" s="15" t="s">
+      <c r="C189" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="D189" s="15" t="str">
+      <c r="D189" s="18" t="str">
         <f>CONCATENATE(C189," (Code: ",B189,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 285-70m without Panel Board (Code: GWDMR185)</v>
       </c>
-      <c r="E189" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F189" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G189" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H189" s="16" t="s">
+      <c r="E189" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F189" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G189" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H189" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I189" s="16">
+      <c r="I189" s="19">
         <v>61559.499999999993</v>
       </c>
-      <c r="J189" s="14">
-        <v>0</v>
-      </c>
-      <c r="K189" s="16">
+      <c r="J189" s="17">
+        <v>0</v>
+      </c>
+      <c r="K189" s="19">
         <f>J189*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L189" s="16">
+      <c r="L189" s="19">
         <f>SUM(I189:K189)</f>
         <v>61559.50</v>
       </c>
@@ -9819,42 +9798,42 @@
       </c>
     </row>
     <row r="191" spans="1:12" ht="12.75">
-      <c r="A191" s="14">
+      <c r="A191" s="17">
         <v>187</v>
       </c>
-      <c r="B191" s="15" t="s">
+      <c r="B191" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C191" s="15" t="s">
+      <c r="C191" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="D191" s="15" t="str">
+      <c r="D191" s="18" t="str">
         <f>CONCATENATE(C191," (Code: ",B191,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 12000-30000 lph, Head 74-29m without Panel Board (Code: GWDMR187)</v>
       </c>
-      <c r="E191" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F191" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G191" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H191" s="16" t="s">
+      <c r="E191" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F191" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H191" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I191" s="16">
+      <c r="I191" s="19">
         <v>61559.499999999993</v>
       </c>
-      <c r="J191" s="14">
-        <v>0</v>
-      </c>
-      <c r="K191" s="16">
+      <c r="J191" s="17">
+        <v>0</v>
+      </c>
+      <c r="K191" s="19">
         <f>J191*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L191" s="16">
+      <c r="L191" s="19">
         <f>SUM(I191:K191)</f>
         <v>61559.50</v>
       </c>
@@ -9901,42 +9880,42 @@
       </c>
     </row>
     <row r="193" spans="1:12" ht="12.75">
-      <c r="A193" s="14">
+      <c r="A193" s="17">
         <v>189</v>
       </c>
-      <c r="B193" s="15" t="s">
+      <c r="B193" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="C193" s="15" t="s">
+      <c r="C193" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="D193" s="15" t="str">
+      <c r="D193" s="18" t="str">
         <f>CONCATENATE(C193," (Code: ",B193,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 6000-18000 lph, Head 112-69m without Panel Board (Code: GWDMR189)</v>
       </c>
-      <c r="E193" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F193" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G193" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H193" s="16" t="s">
+      <c r="E193" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F193" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G193" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H193" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I193" s="16">
+      <c r="I193" s="19">
         <v>67216.005000000005</v>
       </c>
-      <c r="J193" s="14">
-        <v>0</v>
-      </c>
-      <c r="K193" s="16">
+      <c r="J193" s="17">
+        <v>0</v>
+      </c>
+      <c r="K193" s="19">
         <f>J193*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L193" s="16">
+      <c r="L193" s="19">
         <f>SUM(I193:K193)</f>
         <v>67216.005000000005</v>
       </c>
@@ -9983,42 +9962,42 @@
       </c>
     </row>
     <row r="195" spans="1:12" ht="12.75">
-      <c r="A195" s="14">
+      <c r="A195" s="17">
         <v>191</v>
       </c>
-      <c r="B195" s="15" t="s">
+      <c r="B195" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="C195" s="15" t="s">
+      <c r="C195" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="D195" s="15" t="str">
+      <c r="D195" s="18" t="str">
         <f>CONCATENATE(C195," (Code: ",B195,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 158-85m without Panel Board (Code: GWDMR191)</v>
       </c>
-      <c r="E195" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F195" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G195" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H195" s="16" t="s">
+      <c r="E195" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F195" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H195" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I195" s="16">
+      <c r="I195" s="19">
         <v>74094.407999999996</v>
       </c>
-      <c r="J195" s="14">
-        <v>0</v>
-      </c>
-      <c r="K195" s="16">
+      <c r="J195" s="17">
+        <v>0</v>
+      </c>
+      <c r="K195" s="19">
         <f>J195*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L195" s="16">
+      <c r="L195" s="19">
         <f>SUM(I195:K195)</f>
         <v>74094.407999999996</v>
       </c>
@@ -10065,42 +10044,42 @@
       </c>
     </row>
     <row r="197" spans="1:12" ht="12.75">
-      <c r="A197" s="14">
+      <c r="A197" s="17">
         <v>193</v>
       </c>
-      <c r="B197" s="15" t="s">
+      <c r="B197" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="C197" s="15" t="s">
+      <c r="C197" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="D197" s="15" t="str">
+      <c r="D197" s="18" t="str">
         <f>CONCATENATE(C197," (Code: ",B197,")")</f>
         <v>32 A DP switch with indicator modular (MR1017) (Code: GWDMR193)</v>
       </c>
-      <c r="E197" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F197" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G197" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H197" s="16" t="s">
+      <c r="E197" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F197" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G197" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="H197" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="I197" s="16">
+      <c r="I197" s="19">
         <v>432</v>
       </c>
-      <c r="J197" s="14">
-        <v>0</v>
-      </c>
-      <c r="K197" s="16">
+      <c r="J197" s="17">
+        <v>0</v>
+      </c>
+      <c r="K197" s="19">
         <f>J197*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L197" s="16">
+      <c r="L197" s="19">
         <f>SUM(I197:K197)</f>
         <v>432</v>
       </c>
@@ -10117,8 +10096,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>